--- a/output/xlsx/eoss-402.xlsx
+++ b/output/xlsx/eoss-402.xlsx
@@ -3804,7 +3804,7 @@
         <v>46151.32286114583</v>
       </c>
       <c r="D2" s="1">
-        <v>46151.572800925926</v>
+        <v>46151.322800925926</v>
       </c>
       <c r="E2">
         <v>5216</v>
@@ -3911,7 +3911,7 @@
         <v>46151.32317782407</v>
       </c>
       <c r="D3" s="1">
-        <v>46151.57314814815</v>
+        <v>46151.32314814815</v>
       </c>
       <c r="E3">
         <v>5550</v>
@@ -4042,7 +4042,7 @@
         <v>46151.323407476855</v>
       </c>
       <c r="D4" s="1">
-        <v>46151.573379629626</v>
+        <v>46151.323379629626</v>
       </c>
       <c r="E4">
         <v>6043</v>
@@ -4185,7 +4185,7 @@
         <v>46151.32355418982</v>
       </c>
       <c r="D5" s="1">
-        <v>46151.57349537037</v>
+        <v>46151.32349537037</v>
       </c>
       <c r="E5">
         <v>6253</v>
@@ -4328,7 +4328,7 @@
         <v>46151.32378396991</v>
       </c>
       <c r="D6" s="1">
-        <v>46151.57372685185</v>
+        <v>46151.32372685185</v>
       </c>
       <c r="E6">
         <v>6757</v>
@@ -4471,7 +4471,7 @@
         <v>46151.323873229165</v>
       </c>
       <c r="D7" s="1">
-        <v>46151.573842592596</v>
+        <v>46151.323842592596</v>
       </c>
       <c r="E7">
         <v>6949</v>
@@ -4614,7 +4614,7 @@
         <v>46151.32410197917</v>
       </c>
       <c r="D8" s="1">
-        <v>46151.57407407407</v>
+        <v>46151.32407407407</v>
       </c>
       <c r="E8">
         <v>7459</v>
@@ -4757,7 +4757,7 @@
         <v>46151.324248171295</v>
       </c>
       <c r="D9" s="1">
-        <v>46151.57418981481</v>
+        <v>46151.32418981481</v>
       </c>
       <c r="E9">
         <v>7645</v>
@@ -4900,7 +4900,7 @@
         <v>46151.32447856481</v>
       </c>
       <c r="D10" s="1">
-        <v>46151.574421296296</v>
+        <v>46151.324421296296</v>
       </c>
       <c r="E10">
         <v>8182</v>
@@ -5043,7 +5043,7 @@
         <v>46151.324567222226</v>
       </c>
       <c r="D11" s="1">
-        <v>46151.574537037035</v>
+        <v>46151.324537037035</v>
       </c>
       <c r="E11">
         <v>8375</v>
@@ -5186,7 +5186,7 @@
         <v>46151.32479813657</v>
       </c>
       <c r="D12" s="1">
-        <v>46151.57476851852</v>
+        <v>46151.32476851852</v>
       </c>
       <c r="E12">
         <v>8854</v>
@@ -5329,7 +5329,7 @@
         <v>46151.32494484953</v>
       </c>
       <c r="D13" s="1">
-        <v>46151.57488425926</v>
+        <v>46151.32488425926</v>
       </c>
       <c r="E13">
         <v>9034</v>
@@ -5472,7 +5472,7 @@
         <v>46151.32517383102</v>
       </c>
       <c r="D14" s="1">
-        <v>46151.57511574074</v>
+        <v>46151.32511574074</v>
       </c>
       <c r="E14">
         <v>9546</v>
@@ -5615,7 +5615,7 @@
         <v>46151.325492303244</v>
       </c>
       <c r="D15" s="1">
-        <v>46151.57546296297</v>
+        <v>46151.32546296297</v>
       </c>
       <c r="E15">
         <v>10254</v>
@@ -5758,7 +5758,7 @@
         <v>46151.325637685186</v>
       </c>
       <c r="D16" s="1">
-        <v>46151.575578703705</v>
+        <v>46151.325578703705</v>
       </c>
       <c r="E16">
         <v>10431</v>
@@ -5901,7 +5901,7 @@
         <v>46151.32586909722</v>
       </c>
       <c r="D17" s="1">
-        <v>46151.57581018518</v>
+        <v>46151.32581018518</v>
       </c>
       <c r="E17">
         <v>10921</v>
@@ -6044,7 +6044,7 @@
         <v>46151.325955092594</v>
       </c>
       <c r="D18" s="1">
-        <v>46151.57592592593</v>
+        <v>46151.32592592593</v>
       </c>
       <c r="E18">
         <v>11095</v>
@@ -6187,7 +6187,7 @@
         <v>46151.32618622685</v>
       </c>
       <c r="D19" s="1">
-        <v>46151.576157407406</v>
+        <v>46151.326157407406</v>
       </c>
       <c r="E19">
         <v>11624</v>
@@ -6330,7 +6330,7 @@
         <v>46151.32633238426</v>
       </c>
       <c r="D20" s="1">
-        <v>46151.576273148145</v>
+        <v>46151.326273148145</v>
       </c>
       <c r="E20">
         <v>11809</v>
@@ -6473,7 +6473,7 @@
         <v>46151.32656299769</v>
       </c>
       <c r="D21" s="1">
-        <v>46151.57650462963</v>
+        <v>46151.32650462963</v>
       </c>
       <c r="E21">
         <v>12319</v>
@@ -6616,7 +6616,7 @@
         <v>46151.3266509375</v>
       </c>
       <c r="D22" s="1">
-        <v>46151.57662037037</v>
+        <v>46151.32662037037</v>
       </c>
       <c r="E22">
         <v>12500</v>
@@ -6759,7 +6759,7 @@
         <v>46151.32688082176</v>
       </c>
       <c r="D23" s="1">
-        <v>46151.57685185185</v>
+        <v>46151.32685185185</v>
       </c>
       <c r="E23">
         <v>12983</v>
@@ -6902,7 +6902,7 @@
         <v>46151.32702660879</v>
       </c>
       <c r="D24" s="1">
-        <v>46151.57696759259</v>
+        <v>46151.32696759259</v>
       </c>
       <c r="E24">
         <v>13158</v>
@@ -7045,7 +7045,7 @@
         <v>46151.32725787037</v>
       </c>
       <c r="D25" s="1">
-        <v>46151.577199074076</v>
+        <v>46151.327199074076</v>
       </c>
       <c r="E25">
         <v>13706</v>
@@ -7188,7 +7188,7 @@
         <v>46151.32734466435</v>
       </c>
       <c r="D26" s="1">
-        <v>46151.577314814815</v>
+        <v>46151.327314814815</v>
       </c>
       <c r="E26">
         <v>13900</v>
@@ -7331,7 +7331,7 @@
         <v>46151.32757508102</v>
       </c>
       <c r="D27" s="1">
-        <v>46151.5775462963</v>
+        <v>46151.3275462963</v>
       </c>
       <c r="E27">
         <v>14413</v>
@@ -7474,7 +7474,7 @@
         <v>46151.32772141204</v>
       </c>
       <c r="D28" s="1">
-        <v>46151.57766203704</v>
+        <v>46151.32766203704</v>
       </c>
       <c r="E28">
         <v>14607</v>
@@ -7617,7 +7617,7 @@
         <v>46151.32795128472</v>
       </c>
       <c r="D29" s="1">
-        <v>46151.577893518515</v>
+        <v>46151.327893518515</v>
       </c>
       <c r="E29">
         <v>15160</v>
@@ -7760,7 +7760,7 @@
         <v>46151.32804025463</v>
       </c>
       <c r="D30" s="1">
-        <v>46151.57800925926</v>
+        <v>46151.32800925926</v>
       </c>
       <c r="E30">
         <v>15385</v>
@@ -7903,7 +7903,7 @@
         <v>46151.3282703588</v>
       </c>
       <c r="D31" s="1">
-        <v>46151.57824074074</v>
+        <v>46151.32824074074</v>
       </c>
       <c r="E31">
         <v>15938</v>
@@ -8046,7 +8046,7 @@
         <v>46151.32841696759</v>
       </c>
       <c r="D32" s="1">
-        <v>46151.578356481485</v>
+        <v>46151.328356481485</v>
       </c>
       <c r="E32">
         <v>16143</v>
@@ -8189,7 +8189,7 @@
         <v>46151.32864675926</v>
       </c>
       <c r="D33" s="1">
-        <v>46151.57858796296</v>
+        <v>46151.32858796296</v>
       </c>
       <c r="E33">
         <v>16695</v>
@@ -8332,7 +8332,7 @@
         <v>46151.32873394676</v>
       </c>
       <c r="D34" s="1">
-        <v>46151.5787037037</v>
+        <v>46151.3287037037</v>
       </c>
       <c r="E34">
         <v>16889</v>
@@ -8475,7 +8475,7 @@
         <v>46151.328964768516</v>
       </c>
       <c r="D35" s="1">
-        <v>46151.578935185185</v>
+        <v>46151.328935185185</v>
       </c>
       <c r="E35">
         <v>17406</v>
@@ -8618,7 +8618,7 @@
         <v>46151.32911050926</v>
       </c>
       <c r="D36" s="1">
-        <v>46151.579050925924</v>
+        <v>46151.329050925924</v>
       </c>
       <c r="E36">
         <v>17606</v>
@@ -8761,7 +8761,7 @@
         <v>46151.32934246528</v>
       </c>
       <c r="D37" s="1">
-        <v>46151.57928240741</v>
+        <v>46151.32928240741</v>
       </c>
       <c r="E37">
         <v>18126</v>
@@ -8904,7 +8904,7 @@
         <v>46151.329429398145</v>
       </c>
       <c r="D38" s="1">
-        <v>46151.57939814815</v>
+        <v>46151.32939814815</v>
       </c>
       <c r="E38">
         <v>18315</v>
@@ -9047,7 +9047,7 @@
         <v>46151.32966063658</v>
       </c>
       <c r="D39" s="1">
-        <v>46151.57962962963</v>
+        <v>46151.32962962963</v>
       </c>
       <c r="E39">
         <v>18830</v>
@@ -9190,7 +9190,7 @@
         <v>46151.32980435185</v>
       </c>
       <c r="D40" s="1">
-        <v>46151.57974537037</v>
+        <v>46151.32974537037</v>
       </c>
       <c r="E40">
         <v>19026</v>
@@ -9333,7 +9333,7 @@
         <v>46151.33003525463</v>
       </c>
       <c r="D41" s="1">
-        <v>46151.579976851855</v>
+        <v>46151.329976851855</v>
       </c>
       <c r="E41">
         <v>19547</v>
@@ -9476,7 +9476,7 @@
         <v>46151.33012366898</v>
       </c>
       <c r="D42" s="1">
-        <v>46151.580092592594</v>
+        <v>46151.330092592594</v>
       </c>
       <c r="E42">
         <v>19732</v>
@@ -9619,7 +9619,7 @@
         <v>46151.33035311342</v>
       </c>
       <c r="D43" s="1">
-        <v>46151.58032407407</v>
+        <v>46151.33032407407</v>
       </c>
       <c r="E43">
         <v>20253</v>
@@ -9762,7 +9762,7 @@
         <v>46151.33049939815</v>
       </c>
       <c r="D44" s="1">
-        <v>46151.58043981482</v>
+        <v>46151.33043981482</v>
       </c>
       <c r="E44">
         <v>20443</v>
@@ -9905,7 +9905,7 @@
         <v>46151.330730625</v>
       </c>
       <c r="D45" s="1">
-        <v>46151.580671296295</v>
+        <v>46151.330671296295</v>
       </c>
       <c r="E45">
         <v>20970</v>
@@ -10048,7 +10048,7 @@
         <v>46151.3308174537</v>
       </c>
       <c r="D46" s="1">
-        <v>46151.58078703703</v>
+        <v>46151.33078703703</v>
       </c>
       <c r="E46">
         <v>21177</v>
@@ -10191,7 +10191,7 @@
         <v>46151.331047175925</v>
       </c>
       <c r="D47" s="1">
-        <v>46151.58101851852</v>
+        <v>46151.33101851852</v>
       </c>
       <c r="E47">
         <v>21697</v>
@@ -10334,7 +10334,7 @@
         <v>46151.33119266204</v>
       </c>
       <c r="D48" s="1">
-        <v>46151.58113425926</v>
+        <v>46151.33113425926</v>
       </c>
       <c r="E48">
         <v>21904</v>
@@ -10477,7 +10477,7 @@
         <v>46151.33142462963</v>
       </c>
       <c r="D49" s="1">
-        <v>46151.58136574074</v>
+        <v>46151.33136574074</v>
       </c>
       <c r="E49">
         <v>22456</v>
@@ -10620,7 +10620,7 @@
         <v>46151.33151265046</v>
       </c>
       <c r="D50" s="1">
-        <v>46151.58148148148</v>
+        <v>46151.33148148148</v>
       </c>
       <c r="E50">
         <v>22658</v>
@@ -10763,7 +10763,7 @@
         <v>46151.33174241898</v>
       </c>
       <c r="D51" s="1">
-        <v>46151.581712962965</v>
+        <v>46151.331712962965</v>
       </c>
       <c r="E51">
         <v>23178</v>
@@ -10906,7 +10906,7 @@
         <v>46151.331889953704</v>
       </c>
       <c r="D52" s="1">
-        <v>46151.581828703704</v>
+        <v>46151.331828703704</v>
       </c>
       <c r="E52">
         <v>23378</v>
@@ -11049,7 +11049,7 @@
         <v>46151.332119108796</v>
       </c>
       <c r="D53" s="1">
-        <v>46151.58206018519</v>
+        <v>46151.33206018519</v>
       </c>
       <c r="E53">
         <v>23924</v>
@@ -11192,7 +11192,7 @@
         <v>46151.33220664352</v>
       </c>
       <c r="D54" s="1">
-        <v>46151.58217592593</v>
+        <v>46151.33217592593</v>
       </c>
       <c r="E54">
         <v>24139</v>
@@ -11335,7 +11335,7 @@
         <v>46151.332438125</v>
       </c>
       <c r="D55" s="1">
-        <v>46151.582407407404</v>
+        <v>46151.332407407404</v>
       </c>
       <c r="E55">
         <v>24717</v>
@@ -11478,7 +11478,7 @@
         <v>46151.33258274305</v>
       </c>
       <c r="D56" s="1">
-        <v>46151.58252314815</v>
+        <v>46151.33252314815</v>
       </c>
       <c r="E56">
         <v>24923</v>
@@ -11621,7 +11621,7 @@
         <v>46151.33281445602</v>
       </c>
       <c r="D57" s="1">
-        <v>46151.58275462963</v>
+        <v>46151.33275462963</v>
       </c>
       <c r="E57">
         <v>25512</v>
@@ -11764,7 +11764,7 @@
         <v>46151.33290109954</v>
       </c>
       <c r="D58" s="1">
-        <v>46151.582870370374</v>
+        <v>46151.332870370374</v>
       </c>
       <c r="E58">
         <v>25743</v>
@@ -11907,7 +11907,7 @@
         <v>46151.333132430555</v>
       </c>
       <c r="D59" s="1">
-        <v>46151.58310185185</v>
+        <v>46151.33310185185</v>
       </c>
       <c r="E59">
         <v>26343</v>
@@ -12050,7 +12050,7 @@
         <v>46151.33327769676</v>
       </c>
       <c r="D60" s="1">
-        <v>46151.58321759259</v>
+        <v>46151.33321759259</v>
       </c>
       <c r="E60">
         <v>26581</v>
@@ -12193,7 +12193,7 @@
         <v>46151.33351138889</v>
       </c>
       <c r="D61" s="1">
-        <v>46151.583449074074</v>
+        <v>46151.333449074074</v>
       </c>
       <c r="E61">
         <v>27200</v>
@@ -12336,7 +12336,7 @@
         <v>46151.333595833334</v>
       </c>
       <c r="D62" s="1">
-        <v>46151.58356481481</v>
+        <v>46151.33356481481</v>
       </c>
       <c r="E62">
         <v>27433</v>
@@ -12479,7 +12479,7 @@
         <v>46151.33382703704</v>
       </c>
       <c r="D63" s="1">
-        <v>46151.5837962963</v>
+        <v>46151.3337962963</v>
       </c>
       <c r="E63">
         <v>28024</v>
@@ -12622,7 +12622,7 @@
         <v>46151.333972569446</v>
       </c>
       <c r="D64" s="1">
-        <v>46151.58391203704</v>
+        <v>46151.33391203704</v>
       </c>
       <c r="E64">
         <v>28232</v>
@@ -12765,7 +12765,7 @@
         <v>46151.33429042824</v>
       </c>
       <c r="D65" s="1">
-        <v>46151.58425925926</v>
+        <v>46151.33425925926</v>
       </c>
       <c r="E65">
         <v>28975</v>
@@ -12908,7 +12908,7 @@
         <v>46151.334520868055</v>
       </c>
       <c r="D66" s="1">
-        <v>46151.58449074074</v>
+        <v>46151.33449074074</v>
       </c>
       <c r="E66">
         <v>29487</v>
@@ -13051,7 +13051,7 @@
         <v>46151.33466572917</v>
       </c>
       <c r="D67" s="1">
-        <v>46151.58460648148</v>
+        <v>46151.33460648148</v>
       </c>
       <c r="E67">
         <v>29673</v>
@@ -13194,7 +13194,7 @@
         <v>46151.33489809028</v>
       </c>
       <c r="D68" s="1">
-        <v>46151.58483796296</v>
+        <v>46151.33483796296</v>
       </c>
       <c r="E68">
         <v>30224</v>
@@ -13337,7 +13337,7 @@
         <v>46151.33498505787</v>
       </c>
       <c r="D69" s="1">
-        <v>46151.58495370371</v>
+        <v>46151.33495370371</v>
       </c>
       <c r="E69">
         <v>30426</v>
@@ -13480,7 +13480,7 @@
         <v>46151.33521625</v>
       </c>
       <c r="D70" s="1">
-        <v>46151.585185185184</v>
+        <v>46151.335185185184</v>
       </c>
       <c r="E70">
         <v>30972</v>
@@ -13623,7 +13623,7 @@
         <v>46151.33536060185</v>
       </c>
       <c r="D71" s="1">
-        <v>46151.58530092592</v>
+        <v>46151.33530092592</v>
       </c>
       <c r="E71">
         <v>31207</v>
@@ -13766,7 +13766,7 @@
         <v>46151.33559263889</v>
       </c>
       <c r="D72" s="1">
-        <v>46151.58553240741</v>
+        <v>46151.33553240741</v>
       </c>
       <c r="E72">
         <v>31778</v>
@@ -13909,7 +13909,7 @@
         <v>46151.33567888889</v>
       </c>
       <c r="D73" s="1">
-        <v>46151.585648148146</v>
+        <v>46151.335648148146</v>
       </c>
       <c r="E73">
         <v>32011</v>
@@ -14052,7 +14052,7 @@
         <v>46151.335910856484</v>
       </c>
       <c r="D74" s="1">
-        <v>46151.58587962963</v>
+        <v>46151.33587962963</v>
       </c>
       <c r="E74">
         <v>32568</v>
@@ -14195,7 +14195,7 @@
         <v>46151.33605511574</v>
       </c>
       <c r="D75" s="1">
-        <v>46151.58599537037</v>
+        <v>46151.33599537037</v>
       </c>
       <c r="E75">
         <v>32798</v>
@@ -14338,7 +14338,7 @@
         <v>46151.336373032405</v>
       </c>
       <c r="D76" s="1">
-        <v>46151.58634259259</v>
+        <v>46151.33634259259</v>
       </c>
       <c r="E76">
         <v>33599</v>
@@ -14481,7 +14481,7 @@
         <v>46151.336604675926</v>
       </c>
       <c r="D77" s="1">
-        <v>46151.58657407408</v>
+        <v>46151.33657407408</v>
       </c>
       <c r="E77">
         <v>34141</v>
@@ -14624,7 +14624,7 @@
         <v>46151.33674960648</v>
       </c>
       <c r="D78" s="1">
-        <v>46151.586689814816</v>
+        <v>46151.336689814816</v>
       </c>
       <c r="E78">
         <v>34342</v>
@@ -14767,7 +14767,7 @@
         <v>46151.33698075231</v>
       </c>
       <c r="D79" s="1">
-        <v>46151.58692129629</v>
+        <v>46151.33692129629</v>
       </c>
       <c r="E79">
         <v>34929</v>
@@ -14910,7 +14910,7 @@
         <v>46151.337069988425</v>
       </c>
       <c r="D80" s="1">
-        <v>46151.58703703704</v>
+        <v>46151.33703703704</v>
       </c>
       <c r="E80">
         <v>35107</v>
@@ -15053,7 +15053,7 @@
         <v>46151.33729986111</v>
       </c>
       <c r="D81" s="1">
-        <v>46151.58726851852</v>
+        <v>46151.33726851852</v>
       </c>
       <c r="E81">
         <v>35601</v>
@@ -15196,7 +15196,7 @@
         <v>46151.33744444444</v>
       </c>
       <c r="D82" s="1">
-        <v>46151.58738425926</v>
+        <v>46151.33738425926</v>
       </c>
       <c r="E82">
         <v>35789</v>
@@ -15339,7 +15339,7 @@
         <v>46151.337678888885</v>
       </c>
       <c r="D83" s="1">
-        <v>46151.58761574074</v>
+        <v>46151.33761574074</v>
       </c>
       <c r="E83">
         <v>36249</v>
@@ -15482,7 +15482,7 @@
         <v>46151.337764537035</v>
       </c>
       <c r="D84" s="1">
-        <v>46151.58773148148</v>
+        <v>46151.33773148148</v>
       </c>
       <c r="E84">
         <v>36415</v>
@@ -15625,7 +15625,7 @@
         <v>46151.33799467592</v>
       </c>
       <c r="D85" s="1">
-        <v>46151.58796296296</v>
+        <v>46151.33796296296</v>
       </c>
       <c r="E85">
         <v>36902</v>
@@ -15768,7 +15768,7 @@
         <v>46151.33813853009</v>
       </c>
       <c r="D86" s="1">
-        <v>46151.5880787037</v>
+        <v>46151.3380787037</v>
       </c>
       <c r="E86">
         <v>37103</v>
@@ -15911,7 +15911,7 @@
         <v>46151.33837142361</v>
       </c>
       <c r="D87" s="1">
-        <v>46151.58831018519</v>
+        <v>46151.33831018519</v>
       </c>
       <c r="E87">
         <v>37584</v>
@@ -16054,7 +16054,7 @@
         <v>46151.33846236111</v>
       </c>
       <c r="D88" s="1">
-        <v>46151.588425925926</v>
+        <v>46151.338425925926</v>
       </c>
       <c r="E88">
         <v>37786</v>
@@ -16197,7 +16197,7 @@
         <v>46151.33868974537</v>
       </c>
       <c r="D89" s="1">
-        <v>46151.58865740741</v>
+        <v>46151.33865740741</v>
       </c>
       <c r="E89">
         <v>38232</v>
@@ -16340,7 +16340,7 @@
         <v>46151.33883954861</v>
       </c>
       <c r="D90" s="1">
-        <v>46151.58877314815</v>
+        <v>46151.33877314815</v>
       </c>
       <c r="E90">
         <v>38443</v>
@@ -16483,7 +16483,7 @@
         <v>46151.33906540509</v>
       </c>
       <c r="D91" s="1">
-        <v>46151.589004629626</v>
+        <v>46151.339004629626</v>
       </c>
       <c r="E91">
         <v>38895</v>
@@ -16626,7 +16626,7 @@
         <v>46151.3391522338</v>
       </c>
       <c r="D92" s="1">
-        <v>46151.58912037037</v>
+        <v>46151.33912037037</v>
       </c>
       <c r="E92">
         <v>39031</v>
@@ -16769,7 +16769,7 @@
         <v>46151.33938337963</v>
       </c>
       <c r="D93" s="1">
-        <v>46151.58935185185</v>
+        <v>46151.33935185185</v>
       </c>
       <c r="E93">
         <v>39586</v>
@@ -16912,7 +16912,7 @@
         <v>46151.339529212964</v>
       </c>
       <c r="D94" s="1">
-        <v>46151.589467592596</v>
+        <v>46151.339467592596</v>
       </c>
       <c r="E94">
         <v>39816</v>
@@ -17055,7 +17055,7 @@
         <v>46151.339759814815</v>
       </c>
       <c r="D95" s="1">
-        <v>46151.58969907407</v>
+        <v>46151.33969907407</v>
       </c>
       <c r="E95">
         <v>40363</v>
@@ -17198,7 +17198,7 @@
         <v>46151.33984622685</v>
       </c>
       <c r="D96" s="1">
-        <v>46151.58981481481</v>
+        <v>46151.33981481481</v>
       </c>
       <c r="E96">
         <v>40554</v>
@@ -17344,7 +17344,7 @@
         <v>46151.34008005787</v>
       </c>
       <c r="D97" s="1">
-        <v>46151.590046296296</v>
+        <v>46151.340046296296</v>
       </c>
       <c r="E97">
         <v>40892</v>
@@ -17487,7 +17487,7 @@
         <v>46151.3402221412</v>
       </c>
       <c r="D98" s="1">
-        <v>46151.590162037035</v>
+        <v>46151.340162037035</v>
       </c>
       <c r="E98">
         <v>40974</v>
@@ -17630,7 +17630,7 @@
         <v>46151.34045416667</v>
       </c>
       <c r="D99" s="1">
-        <v>46151.59039351852</v>
+        <v>46151.34039351852</v>
       </c>
       <c r="E99">
         <v>41412</v>
@@ -17773,7 +17773,7 @@
         <v>46151.34054025463</v>
       </c>
       <c r="D100" s="1">
-        <v>46151.59050925926</v>
+        <v>46151.34050925926</v>
       </c>
       <c r="E100">
         <v>41488</v>
@@ -17916,7 +17916,7 @@
         <v>46151.34077265047</v>
       </c>
       <c r="D101" s="1">
-        <v>46151.59074074074</v>
+        <v>46151.34074074074</v>
       </c>
       <c r="E101">
         <v>41758</v>
@@ -18059,7 +18059,7 @@
         <v>46151.340917222224</v>
       </c>
       <c r="D102" s="1">
-        <v>46151.59085648148</v>
+        <v>46151.34085648148</v>
       </c>
       <c r="E102">
         <v>41821</v>
@@ -18202,7 +18202,7 @@
         <v>46151.34114841435</v>
       </c>
       <c r="D103" s="1">
-        <v>46151.59108796297</v>
+        <v>46151.34108796297</v>
       </c>
       <c r="E103">
         <v>42111</v>
@@ -18345,7 +18345,7 @@
         <v>46151.34123491898</v>
       </c>
       <c r="D104" s="1">
-        <v>46151.591203703705</v>
+        <v>46151.341203703705</v>
       </c>
       <c r="E104">
         <v>42195</v>
@@ -18488,7 +18488,7 @@
         <v>46151.341466087964</v>
       </c>
       <c r="D105" s="1">
-        <v>46151.59143518518</v>
+        <v>46151.34143518518</v>
       </c>
       <c r="E105">
         <v>42488</v>
@@ -18631,7 +18631,7 @@
         <v>46151.341611550924</v>
       </c>
       <c r="D106" s="1">
-        <v>46151.59155092593</v>
+        <v>46151.34155092593</v>
       </c>
       <c r="E106">
         <v>42573</v>
@@ -18774,7 +18774,7 @@
         <v>46151.3418421875</v>
       </c>
       <c r="D107" s="1">
-        <v>46151.591782407406</v>
+        <v>46151.341782407406</v>
       </c>
       <c r="E107">
         <v>42910</v>
@@ -18917,7 +18917,7 @@
         <v>46151.34192392361</v>
       </c>
       <c r="D108" s="1">
-        <v>46151.591898148145</v>
+        <v>46151.341898148145</v>
       </c>
       <c r="E108">
         <v>43020</v>
@@ -19060,7 +19060,7 @@
         <v>46151.34216097222</v>
       </c>
       <c r="D109" s="1">
-        <v>46151.59212962963</v>
+        <v>46151.34212962963</v>
       </c>
       <c r="E109">
         <v>43342</v>
@@ -19203,7 +19203,7 @@
         <v>46151.34230509259</v>
       </c>
       <c r="D110" s="1">
-        <v>46151.59224537037</v>
+        <v>46151.34224537037</v>
       </c>
       <c r="E110">
         <v>43461</v>
@@ -19346,7 +19346,7 @@
         <v>46151.34253703704</v>
       </c>
       <c r="D111" s="1">
-        <v>46151.59247685185</v>
+        <v>46151.34247685185</v>
       </c>
       <c r="E111">
         <v>43849</v>
@@ -19489,7 +19489,7 @@
         <v>46151.34262309028</v>
       </c>
       <c r="D112" s="1">
-        <v>46151.59259259259</v>
+        <v>46151.34259259259</v>
       </c>
       <c r="E112">
         <v>44002</v>
@@ -19632,7 +19632,7 @@
         <v>46151.342855717594</v>
       </c>
       <c r="D113" s="1">
-        <v>46151.592824074076</v>
+        <v>46151.342824074076</v>
       </c>
       <c r="E113">
         <v>44381</v>
@@ -19775,7 +19775,7 @@
         <v>46151.343</v>
       </c>
       <c r="D114" s="1">
-        <v>46151.592939814815</v>
+        <v>46151.342939814815</v>
       </c>
       <c r="E114">
         <v>44486</v>
@@ -19918,7 +19918,7 @@
         <v>46151.34323381945</v>
       </c>
       <c r="D115" s="1">
-        <v>46151.5931712963</v>
+        <v>46151.3431712963</v>
       </c>
       <c r="E115">
         <v>44826</v>
@@ -20061,7 +20061,7 @@
         <v>46151.34332011574</v>
       </c>
       <c r="D116" s="1">
-        <v>46151.59328703704</v>
+        <v>46151.34328703704</v>
       </c>
       <c r="E116">
         <v>44937</v>
@@ -20204,7 +20204,7 @@
         <v>46151.343549895835</v>
       </c>
       <c r="D117" s="1">
-        <v>46151.593518518515</v>
+        <v>46151.343518518515</v>
       </c>
       <c r="E117">
         <v>45288</v>
@@ -20347,7 +20347,7 @@
         <v>46151.343694282405</v>
       </c>
       <c r="D118" s="1">
-        <v>46151.59363425926</v>
+        <v>46151.34363425926</v>
       </c>
       <c r="E118">
         <v>45388</v>
@@ -20490,7 +20490,7 @@
         <v>46151.34392614583</v>
       </c>
       <c r="D119" s="1">
-        <v>46151.59386574074</v>
+        <v>46151.34386574074</v>
       </c>
       <c r="E119">
         <v>45827</v>
@@ -20633,7 +20633,7 @@
         <v>46151.344030532404</v>
       </c>
       <c r="D120" s="1">
-        <v>46151.593981481485</v>
+        <v>46151.343981481485</v>
       </c>
       <c r="E120">
         <v>45919</v>
@@ -20776,7 +20776,7 @@
         <v>46151.34424436343</v>
       </c>
       <c r="D121" s="1">
-        <v>46151.59421296296</v>
+        <v>46151.34421296296</v>
       </c>
       <c r="E121">
         <v>46214</v>
@@ -20919,7 +20919,7 @@
         <v>46151.34438510417</v>
       </c>
       <c r="D122" s="1">
-        <v>46151.5943287037</v>
+        <v>46151.3443287037</v>
       </c>
       <c r="E122">
         <v>46305</v>
@@ -21062,7 +21062,7 @@
         <v>46151.34461422454</v>
       </c>
       <c r="D123" s="1">
-        <v>46151.594560185185</v>
+        <v>46151.344560185185</v>
       </c>
       <c r="E123">
         <v>46591</v>
@@ -21205,7 +21205,7 @@
         <v>46151.344701539354</v>
       </c>
       <c r="D124" s="1">
-        <v>46151.594675925924</v>
+        <v>46151.344675925924</v>
       </c>
       <c r="E124">
         <v>46680</v>
@@ -21348,7 +21348,7 @@
         <v>46151.34493357639</v>
       </c>
       <c r="D125" s="1">
-        <v>46151.59490740741</v>
+        <v>46151.34490740741</v>
       </c>
       <c r="E125">
         <v>46972</v>
@@ -21491,7 +21491,7 @@
         <v>46151.34507747685</v>
       </c>
       <c r="D126" s="1">
-        <v>46151.59502314815</v>
+        <v>46151.34502314815</v>
       </c>
       <c r="E126">
         <v>47057</v>
@@ -21634,7 +21634,7 @@
         <v>46151.3453094213</v>
       </c>
       <c r="D127" s="1">
-        <v>46151.59525462963</v>
+        <v>46151.34525462963</v>
       </c>
       <c r="E127">
         <v>47404</v>
@@ -21777,7 +21777,7 @@
         <v>46151.345395972225</v>
       </c>
       <c r="D128" s="1">
-        <v>46151.59537037037</v>
+        <v>46151.34537037037</v>
       </c>
       <c r="E128">
         <v>47517</v>
@@ -21920,7 +21920,7 @@
         <v>46151.3456283912</v>
       </c>
       <c r="D129" s="1">
-        <v>46151.595601851855</v>
+        <v>46151.345601851855</v>
       </c>
       <c r="E129">
         <v>47879</v>
@@ -22063,7 +22063,7 @@
         <v>46151.345773217596</v>
       </c>
       <c r="D130" s="1">
-        <v>46151.595717592594</v>
+        <v>46151.345717592594</v>
       </c>
       <c r="E130">
         <v>47975</v>
@@ -22206,7 +22206,7 @@
         <v>46151.34600376157</v>
       </c>
       <c r="D131" s="1">
-        <v>46151.59594907407</v>
+        <v>46151.34594907407</v>
       </c>
       <c r="E131">
         <v>48312</v>
@@ -22349,7 +22349,7 @@
         <v>46151.34609050926</v>
       </c>
       <c r="D132" s="1">
-        <v>46151.59606481482</v>
+        <v>46151.34606481482</v>
       </c>
       <c r="E132">
         <v>48394</v>
@@ -22492,7 +22492,7 @@
         <v>46151.346322233796</v>
       </c>
       <c r="D133" s="1">
-        <v>46151.596296296295</v>
+        <v>46151.346296296295</v>
       </c>
       <c r="E133">
         <v>48732</v>
@@ -22635,7 +22635,7 @@
         <v>46151.34646641204</v>
       </c>
       <c r="D134" s="1">
-        <v>46151.59641203703</v>
+        <v>46151.34641203703</v>
       </c>
       <c r="E134">
         <v>48834</v>
@@ -22778,7 +22778,7 @@
         <v>46151.346698726855</v>
       </c>
       <c r="D135" s="1">
-        <v>46151.59664351852</v>
+        <v>46151.34664351852</v>
       </c>
       <c r="E135">
         <v>49225</v>
@@ -22921,7 +22921,7 @@
         <v>46151.34678555556</v>
       </c>
       <c r="D136" s="1">
-        <v>46151.59675925926</v>
+        <v>46151.34675925926</v>
       </c>
       <c r="E136">
         <v>49416</v>
@@ -23064,7 +23064,7 @@
         <v>46151.34716271991</v>
       </c>
       <c r="D137" s="1">
-        <v>46151.59710648148</v>
+        <v>46151.34710648148</v>
       </c>
       <c r="E137">
         <v>49786</v>
@@ -23207,7 +23207,7 @@
         <v>46151.34739314815</v>
       </c>
       <c r="D138" s="1">
-        <v>46151.597337962965</v>
+        <v>46151.347337962965</v>
       </c>
       <c r="E138">
         <v>50087</v>
@@ -23350,7 +23350,7 @@
         <v>46151.34747983796</v>
       </c>
       <c r="D139" s="1">
-        <v>46151.597453703704</v>
+        <v>46151.347453703704</v>
       </c>
       <c r="E139">
         <v>50153</v>
@@ -23493,7 +23493,7 @@
         <v>46151.34771194444</v>
       </c>
       <c r="D140" s="1">
-        <v>46151.59768518519</v>
+        <v>46151.34768518519</v>
       </c>
       <c r="E140">
         <v>50438</v>
@@ -23636,7 +23636,7 @@
         <v>46151.34785644676</v>
       </c>
       <c r="D141" s="1">
-        <v>46151.59780092593</v>
+        <v>46151.34780092593</v>
       </c>
       <c r="E141">
         <v>50502</v>
@@ -23779,7 +23779,7 @@
         <v>46151.34808849537</v>
       </c>
       <c r="D142" s="1">
-        <v>46151.598032407404</v>
+        <v>46151.348032407404</v>
       </c>
       <c r="E142">
         <v>50898</v>
@@ -23922,7 +23922,7 @@
         <v>46151.34817383102</v>
       </c>
       <c r="D143" s="1">
-        <v>46151.59814814815</v>
+        <v>46151.34814814815</v>
       </c>
       <c r="E143">
         <v>50999</v>
@@ -24065,7 +24065,7 @@
         <v>46151.34840599537</v>
       </c>
       <c r="D144" s="1">
-        <v>46151.59837962963</v>
+        <v>46151.34837962963</v>
       </c>
       <c r="E144">
         <v>51353</v>
@@ -24208,7 +24208,7 @@
         <v>46151.34855134259</v>
       </c>
       <c r="D145" s="1">
-        <v>46151.598495370374</v>
+        <v>46151.348495370374</v>
       </c>
       <c r="E145">
         <v>51445</v>
@@ -24351,7 +24351,7 @@
         <v>46151.34878137732</v>
       </c>
       <c r="D146" s="1">
-        <v>46151.59872685185</v>
+        <v>46151.34872685185</v>
       </c>
       <c r="E146">
         <v>51775</v>
@@ -24494,7 +24494,7 @@
         <v>46151.348871064816</v>
       </c>
       <c r="D147" s="1">
-        <v>46151.59884259259</v>
+        <v>46151.34884259259</v>
       </c>
       <c r="E147">
         <v>51857</v>
@@ -24637,7 +24637,7 @@
         <v>46151.34910254629</v>
       </c>
       <c r="D148" s="1">
-        <v>46151.599074074074</v>
+        <v>46151.349074074074</v>
       </c>
       <c r="E148">
         <v>52173</v>
@@ -24780,7 +24780,7 @@
         <v>46151.349244791665</v>
       </c>
       <c r="D149" s="1">
-        <v>46151.59918981481</v>
+        <v>46151.34918981481</v>
       </c>
       <c r="E149">
         <v>52269</v>
@@ -24923,7 +24923,7 @@
         <v>46151.34947706018</v>
       </c>
       <c r="D150" s="1">
-        <v>46151.5994212963</v>
+        <v>46151.3494212963</v>
       </c>
       <c r="E150">
         <v>52602</v>
@@ -25066,7 +25066,7 @@
         <v>46151.34956310185</v>
       </c>
       <c r="D151" s="1">
-        <v>46151.59953703704</v>
+        <v>46151.34953703704</v>
       </c>
       <c r="E151">
         <v>52680</v>
@@ -25209,7 +25209,7 @@
         <v>46151.34979479167</v>
       </c>
       <c r="D152" s="1">
-        <v>46151.59976851852</v>
+        <v>46151.34976851852</v>
       </c>
       <c r="E152">
         <v>53018</v>
@@ -25352,7 +25352,7 @@
         <v>46151.3499403125</v>
       </c>
       <c r="D153" s="1">
-        <v>46151.59988425926</v>
+        <v>46151.34988425926</v>
       </c>
       <c r="E153">
         <v>53107</v>
@@ -25495,7 +25495,7 @@
         <v>46151.35017075232</v>
       </c>
       <c r="D154" s="1">
-        <v>46151.60011574074</v>
+        <v>46151.35011574074</v>
       </c>
       <c r="E154">
         <v>53399</v>
@@ -25638,7 +25638,7 @@
         <v>46151.35026008102</v>
       </c>
       <c r="D155" s="1">
-        <v>46151.60023148148</v>
+        <v>46151.35023148148</v>
       </c>
       <c r="E155">
         <v>53474</v>
@@ -25781,7 +25781,7 @@
         <v>46151.35048952547</v>
       </c>
       <c r="D156" s="1">
-        <v>46151.60046296296</v>
+        <v>46151.35046296296</v>
       </c>
       <c r="E156">
         <v>53796</v>
@@ -25924,7 +25924,7 @@
         <v>46151.350644224534</v>
       </c>
       <c r="D157" s="1">
-        <v>46151.60057870371</v>
+        <v>46151.35057870371</v>
       </c>
       <c r="E157">
         <v>53884</v>
@@ -26067,7 +26067,7 @@
         <v>46151.35086534722</v>
       </c>
       <c r="D158" s="1">
-        <v>46151.600810185184</v>
+        <v>46151.350810185184</v>
       </c>
       <c r="E158">
         <v>54217</v>
@@ -26210,7 +26210,7 @@
         <v>46151.35097568287</v>
       </c>
       <c r="D159" s="1">
-        <v>46151.60092592592</v>
+        <v>46151.35092592592</v>
       </c>
       <c r="E159">
         <v>54334</v>
@@ -26353,7 +26353,7 @@
         <v>46151.35118408565</v>
       </c>
       <c r="D160" s="1">
-        <v>46151.60115740741</v>
+        <v>46151.35115740741</v>
       </c>
       <c r="E160">
         <v>54646</v>
@@ -26496,7 +26496,7 @@
         <v>46151.35132861111</v>
       </c>
       <c r="D161" s="1">
-        <v>46151.601273148146</v>
+        <v>46151.351273148146</v>
       </c>
       <c r="E161">
         <v>54717</v>
@@ -26639,7 +26639,7 @@
         <v>46151.35155998843</v>
       </c>
       <c r="D162" s="1">
-        <v>46151.60150462963</v>
+        <v>46151.35150462963</v>
       </c>
       <c r="E162">
         <v>55020</v>
@@ -26782,7 +26782,7 @@
         <v>46151.35165116898</v>
       </c>
       <c r="D163" s="1">
-        <v>46151.60162037037</v>
+        <v>46151.35162037037</v>
       </c>
       <c r="E163">
         <v>55107</v>
@@ -26925,7 +26925,7 @@
         <v>46151.35187886574</v>
       </c>
       <c r="D164" s="1">
-        <v>46151.601851851854</v>
+        <v>46151.351851851854</v>
       </c>
       <c r="E164">
         <v>55396</v>
@@ -27068,7 +27068,7 @@
         <v>46151.352023287036</v>
       </c>
       <c r="D165" s="1">
-        <v>46151.60196759259</v>
+        <v>46151.35196759259</v>
       </c>
       <c r="E165">
         <v>55462</v>
@@ -27211,7 +27211,7 @@
         <v>46151.35225423611</v>
       </c>
       <c r="D166" s="1">
-        <v>46151.60219907408</v>
+        <v>46151.35219907408</v>
       </c>
       <c r="E166">
         <v>55805</v>
@@ -27354,7 +27354,7 @@
         <v>46151.352364583334</v>
       </c>
       <c r="D167" s="1">
-        <v>46151.602314814816</v>
+        <v>46151.352314814816</v>
       </c>
       <c r="E167">
         <v>55907</v>
@@ -27497,7 +27497,7 @@
         <v>46151.352572881944</v>
       </c>
       <c r="D168" s="1">
-        <v>46151.60254629629</v>
+        <v>46151.35254629629</v>
       </c>
       <c r="E168">
         <v>56222</v>
@@ -27640,7 +27640,7 @@
         <v>46151.35271959491</v>
       </c>
       <c r="D169" s="1">
-        <v>46151.60266203704</v>
+        <v>46151.35266203704</v>
       </c>
       <c r="E169">
         <v>56309</v>
@@ -27783,7 +27783,7 @@
         <v>46151.352950023145</v>
       </c>
       <c r="D170" s="1">
-        <v>46151.60289351852</v>
+        <v>46151.35289351852</v>
       </c>
       <c r="E170">
         <v>56666</v>
@@ -27926,7 +27926,7 @@
         <v>46151.35303866898</v>
       </c>
       <c r="D171" s="1">
-        <v>46151.60300925926</v>
+        <v>46151.35300925926</v>
       </c>
       <c r="E171">
         <v>56753</v>
@@ -28069,7 +28069,7 @@
         <v>46151.35326726852</v>
       </c>
       <c r="D172" s="1">
-        <v>46151.60324074074</v>
+        <v>46151.35324074074</v>
       </c>
       <c r="E172">
         <v>57093</v>
@@ -28212,7 +28212,7 @@
         <v>46151.35341206018</v>
       </c>
       <c r="D173" s="1">
-        <v>46151.60335648148</v>
+        <v>46151.35335648148</v>
       </c>
       <c r="E173">
         <v>57187</v>
@@ -28355,7 +28355,7 @@
         <v>46151.35373008102</v>
       </c>
       <c r="D174" s="1">
-        <v>46151.6037037037</v>
+        <v>46151.3537037037</v>
       </c>
       <c r="E174">
         <v>57643</v>
@@ -28498,7 +28498,7 @@
         <v>46151.35396222222</v>
       </c>
       <c r="D175" s="1">
-        <v>46151.60393518519</v>
+        <v>46151.35393518519</v>
       </c>
       <c r="E175">
         <v>57993</v>
@@ -28641,7 +28641,7 @@
         <v>46151.35410657407</v>
       </c>
       <c r="D176" s="1">
-        <v>46151.604050925926</v>
+        <v>46151.354050925926</v>
       </c>
       <c r="E176">
         <v>58096</v>
@@ -28784,7 +28784,7 @@
         <v>46151.35433833333</v>
       </c>
       <c r="D177" s="1">
-        <v>46151.60428240741</v>
+        <v>46151.35428240741</v>
       </c>
       <c r="E177">
         <v>58432</v>
@@ -28927,7 +28927,7 @@
         <v>46151.35442523148</v>
       </c>
       <c r="D178" s="1">
-        <v>46151.60439814815</v>
+        <v>46151.35439814815</v>
       </c>
       <c r="E178">
         <v>58555</v>
@@ -29070,7 +29070,7 @@
         <v>46151.35465710648</v>
       </c>
       <c r="D179" s="1">
-        <v>46151.604629629626</v>
+        <v>46151.354629629626</v>
       </c>
       <c r="E179">
         <v>59000</v>
@@ -29213,7 +29213,7 @@
         <v>46151.35480113426</v>
       </c>
       <c r="D180" s="1">
-        <v>46151.60474537037</v>
+        <v>46151.35474537037</v>
       </c>
       <c r="E180">
         <v>59153</v>
@@ -29356,7 +29356,7 @@
         <v>46151.35503290509</v>
       </c>
       <c r="D181" s="1">
-        <v>46151.60497685185</v>
+        <v>46151.35497685185</v>
       </c>
       <c r="E181">
         <v>59574</v>
@@ -29499,7 +29499,7 @@
         <v>46151.35511957176</v>
       </c>
       <c r="D182" s="1">
-        <v>46151.605092592596</v>
+        <v>46151.355092592596</v>
       </c>
       <c r="E182">
         <v>59699</v>
@@ -29642,7 +29642,7 @@
         <v>46151.35535099537</v>
       </c>
       <c r="D183" s="1">
-        <v>46151.60532407407</v>
+        <v>46151.35532407407</v>
       </c>
       <c r="E183">
         <v>60068</v>
@@ -29785,7 +29785,7 @@
         <v>46151.35549606482</v>
       </c>
       <c r="D184" s="1">
-        <v>46151.60543981481</v>
+        <v>46151.35543981481</v>
       </c>
       <c r="E184">
         <v>60201</v>
@@ -29928,7 +29928,7 @@
         <v>46151.35572753472</v>
       </c>
       <c r="D185" s="1">
-        <v>46151.605671296296</v>
+        <v>46151.355671296296</v>
       </c>
       <c r="E185">
         <v>60623</v>
@@ -30071,7 +30071,7 @@
         <v>46151.35581443287</v>
       </c>
       <c r="D186" s="1">
-        <v>46151.605787037035</v>
+        <v>46151.355787037035</v>
       </c>
       <c r="E186">
         <v>60769</v>
@@ -30214,7 +30214,7 @@
         <v>46151.35604653935</v>
       </c>
       <c r="D187" s="1">
-        <v>46151.60601851852</v>
+        <v>46151.35601851852</v>
       </c>
       <c r="E187">
         <v>61127</v>
@@ -30357,7 +30357,7 @@
         <v>46151.35619054398</v>
       </c>
       <c r="D188" s="1">
-        <v>46151.60613425926</v>
+        <v>46151.35613425926</v>
       </c>
       <c r="E188">
         <v>61234</v>
@@ -30500,7 +30500,7 @@
         <v>46151.356422523146</v>
       </c>
       <c r="D189" s="1">
-        <v>46151.60636574074</v>
+        <v>46151.35636574074</v>
       </c>
       <c r="E189">
         <v>61555</v>
@@ -30643,7 +30643,7 @@
         <v>46151.356507743054</v>
       </c>
       <c r="D190" s="1">
-        <v>46151.60648148148</v>
+        <v>46151.35648148148</v>
       </c>
       <c r="E190">
         <v>61666</v>
@@ -30786,7 +30786,7 @@
         <v>46151.3567402662</v>
       </c>
       <c r="D191" s="1">
-        <v>46151.60671296297</v>
+        <v>46151.35671296297</v>
       </c>
       <c r="E191">
         <v>62034</v>
@@ -30929,7 +30929,7 @@
         <v>46151.356884375</v>
       </c>
       <c r="D192" s="1">
-        <v>46151.606828703705</v>
+        <v>46151.356828703705</v>
       </c>
       <c r="E192">
         <v>62114</v>
@@ -31072,7 +31072,7 @@
         <v>46151.357117962965</v>
       </c>
       <c r="D193" s="1">
-        <v>46151.60706018518</v>
+        <v>46151.35706018518</v>
       </c>
       <c r="E193">
         <v>62475</v>
@@ -31215,7 +31215,7 @@
         <v>46151.357202280094</v>
       </c>
       <c r="D194" s="1">
-        <v>46151.60717592593</v>
+        <v>46151.35717592593</v>
       </c>
       <c r="E194">
         <v>62552</v>
@@ -31358,7 +31358,7 @@
         <v>46151.357438287036</v>
       </c>
       <c r="D195" s="1">
-        <v>46151.607407407406</v>
+        <v>46151.357407407406</v>
       </c>
       <c r="E195">
         <v>62885</v>
@@ -31501,7 +31501,7 @@
         <v>46151.35757855324</v>
       </c>
       <c r="D196" s="1">
-        <v>46151.607523148145</v>
+        <v>46151.357523148145</v>
       </c>
       <c r="E196">
         <v>62974</v>
@@ -31644,7 +31644,7 @@
         <v>46151.35781164352</v>
       </c>
       <c r="D197" s="1">
-        <v>46151.60775462963</v>
+        <v>46151.35775462963</v>
       </c>
       <c r="E197">
         <v>63298</v>
@@ -31787,7 +31787,7 @@
         <v>46151.35789730324</v>
       </c>
       <c r="D198" s="1">
-        <v>46151.60787037037</v>
+        <v>46151.35787037037</v>
       </c>
       <c r="E198">
         <v>63394</v>
@@ -31930,7 +31930,7 @@
         <v>46151.35813037037</v>
       </c>
       <c r="D199" s="1">
-        <v>46151.60810185185</v>
+        <v>46151.35810185185</v>
       </c>
       <c r="E199">
         <v>63704</v>
@@ -32073,7 +32073,7 @@
         <v>46151.358274039354</v>
       </c>
       <c r="D200" s="1">
-        <v>46151.60821759259</v>
+        <v>46151.35821759259</v>
       </c>
       <c r="E200">
         <v>63800</v>
@@ -32216,7 +32216,7 @@
         <v>46151.358506666664</v>
       </c>
       <c r="D201" s="1">
-        <v>46151.608449074076</v>
+        <v>46151.358449074076</v>
       </c>
       <c r="E201">
         <v>64129</v>
@@ -32359,7 +32359,7 @@
         <v>46151.35859082176</v>
       </c>
       <c r="D202" s="1">
-        <v>46151.608564814815</v>
+        <v>46151.358564814815</v>
       </c>
       <c r="E202">
         <v>64217</v>
@@ -32502,7 +32502,7 @@
         <v>46151.3588233912</v>
       </c>
       <c r="D203" s="1">
-        <v>46151.6087962963</v>
+        <v>46151.3587962963</v>
       </c>
       <c r="E203">
         <v>64538</v>
@@ -32645,7 +32645,7 @@
         <v>46151.35896841435</v>
       </c>
       <c r="D204" s="1">
-        <v>46151.60891203704</v>
+        <v>46151.35891203704</v>
       </c>
       <c r="E204">
         <v>64600</v>
@@ -32788,7 +32788,7 @@
         <v>46151.359201631945</v>
       </c>
       <c r="D205" s="1">
-        <v>46151.609143518515</v>
+        <v>46151.359143518515</v>
       </c>
       <c r="E205">
         <v>64901</v>
@@ -32931,7 +32931,7 @@
         <v>46151.35928667824</v>
       </c>
       <c r="D206" s="1">
-        <v>46151.60925925926</v>
+        <v>46151.35925925926</v>
       </c>
       <c r="E206">
         <v>64962</v>
@@ -33074,7 +33074,7 @@
         <v>46151.3595184838</v>
       </c>
       <c r="D207" s="1">
-        <v>46151.60949074074</v>
+        <v>46151.35949074074</v>
       </c>
       <c r="E207">
         <v>65256</v>
@@ -33217,7 +33217,7 @@
         <v>46151.35966212963</v>
       </c>
       <c r="D208" s="1">
-        <v>46151.609606481485</v>
+        <v>46151.359606481485</v>
       </c>
       <c r="E208">
         <v>65346</v>
@@ -33360,7 +33360,7 @@
         <v>46151.35989491898</v>
       </c>
       <c r="D209" s="1">
-        <v>46151.60983796296</v>
+        <v>46151.35983796296</v>
       </c>
       <c r="E209">
         <v>65660</v>
@@ -33503,7 +33503,7 @@
         <v>46151.359981180554</v>
       </c>
       <c r="D210" s="1">
-        <v>46151.6099537037</v>
+        <v>46151.3599537037</v>
       </c>
       <c r="E210">
         <v>65744</v>
@@ -33646,7 +33646,7 @@
         <v>46151.360212974534</v>
       </c>
       <c r="D211" s="1">
-        <v>46151.610185185185</v>
+        <v>46151.360185185185</v>
       </c>
       <c r="E211">
         <v>66056</v>
@@ -33789,7 +33789,7 @@
         <v>46151.36035686343</v>
       </c>
       <c r="D212" s="1">
-        <v>46151.610300925924</v>
+        <v>46151.360300925924</v>
       </c>
       <c r="E212">
         <v>66144</v>
@@ -33932,7 +33932,7 @@
         <v>46151.36058927084</v>
       </c>
       <c r="D213" s="1">
-        <v>46151.61053240741</v>
+        <v>46151.36053240741</v>
       </c>
       <c r="E213">
         <v>66498</v>
@@ -34075,7 +34075,7 @@
         <v>46151.36067454861</v>
       </c>
       <c r="D214" s="1">
-        <v>46151.61064814815</v>
+        <v>46151.36064814815</v>
       </c>
       <c r="E214">
         <v>66592</v>
@@ -34218,7 +34218,7 @@
         <v>46151.36090824074</v>
       </c>
       <c r="D215" s="1">
-        <v>46151.61087962963</v>
+        <v>46151.36087962963</v>
       </c>
       <c r="E215">
         <v>66951</v>
@@ -34361,7 +34361,7 @@
         <v>46151.361054409725</v>
       </c>
       <c r="D216" s="1">
-        <v>46151.61099537037</v>
+        <v>46151.36099537037</v>
       </c>
       <c r="E216">
         <v>67058</v>
@@ -34504,7 +34504,7 @@
         <v>46151.36128451389</v>
       </c>
       <c r="D217" s="1">
-        <v>46151.611226851855</v>
+        <v>46151.361226851855</v>
       </c>
       <c r="E217">
         <v>67459</v>
@@ -34647,7 +34647,7 @@
         <v>46151.361369652775</v>
       </c>
       <c r="D218" s="1">
-        <v>46151.611342592594</v>
+        <v>46151.361342592594</v>
       </c>
       <c r="E218">
         <v>67576</v>
@@ -34790,7 +34790,7 @@
         <v>46151.36160230324</v>
       </c>
       <c r="D219" s="1">
-        <v>46151.61157407407</v>
+        <v>46151.36157407407</v>
       </c>
       <c r="E219">
         <v>67973</v>
@@ -34933,7 +34933,7 @@
         <v>46151.36174608796</v>
       </c>
       <c r="D220" s="1">
-        <v>46151.61168981482</v>
+        <v>46151.36168981482</v>
       </c>
       <c r="E220">
         <v>68070</v>
@@ -35076,7 +35076,7 @@
         <v>46151.36197928241</v>
       </c>
       <c r="D221" s="1">
-        <v>46151.611921296295</v>
+        <v>46151.361921296295</v>
       </c>
       <c r="E221">
         <v>68428</v>
@@ -35219,7 +35219,7 @@
         <v>46151.36206451389</v>
       </c>
       <c r="D222" s="1">
-        <v>46151.61203703703</v>
+        <v>46151.36203703703</v>
       </c>
       <c r="E222">
         <v>68525</v>
@@ -35362,7 +35362,7 @@
         <v>46151.3622962963</v>
       </c>
       <c r="D223" s="1">
-        <v>46151.61226851852</v>
+        <v>46151.36226851852</v>
       </c>
       <c r="E223">
         <v>68884</v>
@@ -35505,7 +35505,7 @@
         <v>46151.36244037037</v>
       </c>
       <c r="D224" s="1">
-        <v>46151.61238425926</v>
+        <v>46151.36238425926</v>
       </c>
       <c r="E224">
         <v>68961</v>
@@ -35648,7 +35648,7 @@
         <v>46151.362672407406</v>
       </c>
       <c r="D225" s="1">
-        <v>46151.61261574074</v>
+        <v>46151.36261574074</v>
       </c>
       <c r="E225">
         <v>69324</v>
@@ -35791,7 +35791,7 @@
         <v>46151.3627587963</v>
       </c>
       <c r="D226" s="1">
-        <v>46151.61273148148</v>
+        <v>46151.36273148148</v>
       </c>
       <c r="E226">
         <v>69421</v>
@@ -35934,7 +35934,7 @@
         <v>46151.36299101852</v>
       </c>
       <c r="D227" s="1">
-        <v>46151.612962962965</v>
+        <v>46151.362962962965</v>
       </c>
       <c r="E227">
         <v>69763</v>
@@ -36077,7 +36077,7 @@
         <v>46151.36336880787</v>
       </c>
       <c r="D228" s="1">
-        <v>46151.61331018519</v>
+        <v>46151.36331018519</v>
       </c>
       <c r="E228">
         <v>70212</v>
@@ -36220,7 +36220,7 @@
         <v>46151.363456273146</v>
       </c>
       <c r="D229" s="1">
-        <v>46151.61342592593</v>
+        <v>46151.36342592593</v>
       </c>
       <c r="E229">
         <v>70308</v>
@@ -36363,7 +36363,7 @@
         <v>46151.36368574074</v>
       </c>
       <c r="D230" s="1">
-        <v>46151.613657407404</v>
+        <v>46151.363657407404</v>
       </c>
       <c r="E230">
         <v>70660</v>
@@ -36506,7 +36506,7 @@
         <v>46151.363830856484</v>
       </c>
       <c r="D231" s="1">
-        <v>46151.61377314815</v>
+        <v>46151.36377314815</v>
       </c>
       <c r="E231">
         <v>70764</v>
@@ -36649,7 +36649,7 @@
         <v>46151.364061643515</v>
       </c>
       <c r="D232" s="1">
-        <v>46151.61400462963</v>
+        <v>46151.36400462963</v>
       </c>
       <c r="E232">
         <v>71130</v>
@@ -36792,7 +36792,7 @@
         <v>46151.36415054398</v>
       </c>
       <c r="D233" s="1">
-        <v>46151.614120370374</v>
+        <v>46151.364120370374</v>
       </c>
       <c r="E233">
         <v>71254</v>
@@ -36935,7 +36935,7 @@
         <v>46151.36437940972</v>
       </c>
       <c r="D234" s="1">
-        <v>46151.61435185185</v>
+        <v>46151.36435185185</v>
       </c>
       <c r="E234">
         <v>71599</v>
@@ -37078,7 +37078,7 @@
         <v>46151.364524386576</v>
       </c>
       <c r="D235" s="1">
-        <v>46151.61446759259</v>
+        <v>46151.36446759259</v>
       </c>
       <c r="E235">
         <v>71701</v>
@@ -37221,7 +37221,7 @@
         <v>46151.364755752315</v>
       </c>
       <c r="D236" s="1">
-        <v>46151.614699074074</v>
+        <v>46151.364699074074</v>
       </c>
       <c r="E236">
         <v>72063</v>
@@ -37364,7 +37364,7 @@
         <v>46151.36484209491</v>
       </c>
       <c r="D237" s="1">
-        <v>46151.61481481481</v>
+        <v>46151.36481481481</v>
       </c>
       <c r="E237">
         <v>72152</v>
@@ -37507,7 +37507,7 @@
         <v>46151.36507428241</v>
       </c>
       <c r="D238" s="1">
-        <v>46151.6150462963</v>
+        <v>46151.3650462963</v>
       </c>
       <c r="E238">
         <v>72497</v>
@@ -37650,7 +37650,7 @@
         <v>46151.36521881945</v>
       </c>
       <c r="D239" s="1">
-        <v>46151.61516203704</v>
+        <v>46151.36516203704</v>
       </c>
       <c r="E239">
         <v>72570</v>
@@ -37949,7 +37949,7 @@
         <v>46151.36548140046</v>
       </c>
       <c r="D2" s="1">
-        <v>46151.61539351852</v>
+        <v>46151.36539351852</v>
       </c>
       <c r="E2">
         <v>71790</v>
@@ -38056,7 +38056,7 @@
         <v>46151.36553696759</v>
       </c>
       <c r="D3" s="1">
-        <v>46151.61550925926</v>
+        <v>46151.36550925926</v>
       </c>
       <c r="E3">
         <v>71231</v>
@@ -38187,7 +38187,7 @@
         <v>46151.365769375</v>
       </c>
       <c r="D4" s="1">
-        <v>46151.61574074074</v>
+        <v>46151.36574074074</v>
       </c>
       <c r="E4">
         <v>70319</v>
@@ -38330,7 +38330,7 @@
         <v>46151.366146643515</v>
       </c>
       <c r="D5" s="1">
-        <v>46151.61608796296</v>
+        <v>46151.36608796296</v>
       </c>
       <c r="E5">
         <v>68780</v>
@@ -38473,7 +38473,7 @@
         <v>46151.366232037035</v>
       </c>
       <c r="D6" s="1">
-        <v>46151.61620370371</v>
+        <v>46151.36620370371</v>
       </c>
       <c r="E6">
         <v>68236</v>
@@ -38616,7 +38616,7 @@
         <v>46151.36646131944</v>
       </c>
       <c r="D7" s="1">
-        <v>46151.616435185184</v>
+        <v>46151.366435185184</v>
       </c>
       <c r="E7">
         <v>67373</v>
@@ -38759,7 +38759,7 @@
         <v>46151.366607986114</v>
       </c>
       <c r="D8" s="1">
-        <v>46151.61655092592</v>
+        <v>46151.36655092592</v>
       </c>
       <c r="E8">
         <v>66897</v>
@@ -38902,7 +38902,7 @@
         <v>46151.36683721065</v>
       </c>
       <c r="D9" s="1">
-        <v>46151.61678240741</v>
+        <v>46151.36678240741</v>
       </c>
       <c r="E9">
         <v>66030</v>
@@ -39045,7 +39045,7 @@
         <v>46151.36692590278</v>
       </c>
       <c r="D10" s="1">
-        <v>46151.616898148146</v>
+        <v>46151.366898148146</v>
       </c>
       <c r="E10">
         <v>65464</v>
@@ -39188,7 +39188,7 @@
         <v>46151.367155949076</v>
       </c>
       <c r="D11" s="1">
-        <v>46151.61712962963</v>
+        <v>46151.36712962963</v>
       </c>
       <c r="E11">
         <v>64437</v>
@@ -39331,7 +39331,7 @@
         <v>46151.367301921295</v>
       </c>
       <c r="D12" s="1">
-        <v>46151.61724537037</v>
+        <v>46151.36724537037</v>
       </c>
       <c r="E12">
         <v>63913</v>
@@ -39474,7 +39474,7 @@
         <v>46151.3675315162</v>
       </c>
       <c r="D13" s="1">
-        <v>46151.617476851854</v>
+        <v>46151.367476851854</v>
       </c>
       <c r="E13">
         <v>62986</v>
@@ -39617,7 +39617,7 @@
         <v>46151.367620034725</v>
       </c>
       <c r="D14" s="1">
-        <v>46151.61759259259</v>
+        <v>46151.36759259259</v>
       </c>
       <c r="E14">
         <v>62530</v>
@@ -39760,7 +39760,7 @@
         <v>46151.367851863426</v>
       </c>
       <c r="D15" s="1">
-        <v>46151.61782407408</v>
+        <v>46151.36782407408</v>
       </c>
       <c r="E15">
         <v>61831</v>
@@ -39903,7 +39903,7 @@
         <v>46151.36799722222</v>
       </c>
       <c r="D16" s="1">
-        <v>46151.617939814816</v>
+        <v>46151.367939814816</v>
       </c>
       <c r="E16">
         <v>61384</v>
@@ -40046,7 +40046,7 @@
         <v>46151.36822974537</v>
       </c>
       <c r="D17" s="1">
-        <v>46151.61817129629</v>
+        <v>46151.36817129629</v>
       </c>
       <c r="E17">
         <v>60645</v>
@@ -40189,7 +40189,7 @@
         <v>46151.36831479167</v>
       </c>
       <c r="D18" s="1">
-        <v>46151.61828703704</v>
+        <v>46151.36828703704</v>
       </c>
       <c r="E18">
         <v>60215</v>
@@ -40332,7 +40332,7 @@
         <v>46151.368548645834</v>
       </c>
       <c r="D19" s="1">
-        <v>46151.61851851852</v>
+        <v>46151.36851851852</v>
       </c>
       <c r="E19">
         <v>59509</v>
@@ -40475,7 +40475,7 @@
         <v>46151.36869244213</v>
       </c>
       <c r="D20" s="1">
-        <v>46151.61863425926</v>
+        <v>46151.36863425926</v>
       </c>
       <c r="E20">
         <v>59090</v>
@@ -40618,7 +40618,7 @@
         <v>46151.3689243287</v>
       </c>
       <c r="D21" s="1">
-        <v>46151.61886574074</v>
+        <v>46151.36886574074</v>
       </c>
       <c r="E21">
         <v>58358</v>
@@ -40761,7 +40761,7 @@
         <v>46151.36900895833</v>
       </c>
       <c r="D22" s="1">
-        <v>46151.61898148148</v>
+        <v>46151.36898148148</v>
       </c>
       <c r="E22">
         <v>57910</v>
@@ -40904,7 +40904,7 @@
         <v>46151.369242534725</v>
       </c>
       <c r="D23" s="1">
-        <v>46151.61921296296</v>
+        <v>46151.36921296296</v>
       </c>
       <c r="E23">
         <v>57201</v>
@@ -41047,7 +41047,7 @@
         <v>46151.369385405094</v>
       </c>
       <c r="D24" s="1">
-        <v>46151.6193287037</v>
+        <v>46151.3693287037</v>
       </c>
       <c r="E24">
         <v>56813</v>
@@ -41190,7 +41190,7 @@
         <v>46151.36961873843</v>
       </c>
       <c r="D25" s="1">
-        <v>46151.61956018519</v>
+        <v>46151.36956018519</v>
       </c>
       <c r="E25">
         <v>56192</v>
@@ -41333,7 +41333,7 @@
         <v>46151.36970422454</v>
       </c>
       <c r="D26" s="1">
-        <v>46151.619675925926</v>
+        <v>46151.369675925926</v>
       </c>
       <c r="E26">
         <v>55820</v>
@@ -41476,7 +41476,7 @@
         <v>46151.36993783565</v>
       </c>
       <c r="D27" s="1">
-        <v>46151.61990740741</v>
+        <v>46151.36990740741</v>
       </c>
       <c r="E27">
         <v>55252</v>
@@ -41619,7 +41619,7 @@
         <v>46151.370080277775</v>
       </c>
       <c r="D28" s="1">
-        <v>46151.62002314815</v>
+        <v>46151.37002314815</v>
       </c>
       <c r="E28">
         <v>54895</v>
@@ -41762,7 +41762,7 @@
         <v>46151.37031394676</v>
       </c>
       <c r="D29" s="1">
-        <v>46151.620254629626</v>
+        <v>46151.370254629626</v>
       </c>
       <c r="E29">
         <v>54343</v>
@@ -41905,7 +41905,7 @@
         <v>46151.370397997685</v>
       </c>
       <c r="D30" s="1">
-        <v>46151.62037037037</v>
+        <v>46151.37037037037</v>
       </c>
       <c r="E30">
         <v>54006</v>
@@ -42048,7 +42048,7 @@
         <v>46151.37062753472</v>
       </c>
       <c r="D31" s="1">
-        <v>46151.62060185185</v>
+        <v>46151.37060185185</v>
       </c>
       <c r="E31">
         <v>53476</v>
@@ -42191,7 +42191,7 @@
         <v>46151.370773877316</v>
       </c>
       <c r="D32" s="1">
-        <v>46151.620717592596</v>
+        <v>46151.370717592596</v>
       </c>
       <c r="E32">
         <v>53101</v>
@@ -42334,7 +42334,7 @@
         <v>46151.371009456016</v>
       </c>
       <c r="D33" s="1">
-        <v>46151.62094907407</v>
+        <v>46151.37094907407</v>
       </c>
       <c r="E33">
         <v>52572</v>
@@ -42477,7 +42477,7 @@
         <v>46151.371092824076</v>
       </c>
       <c r="D34" s="1">
-        <v>46151.62106481481</v>
+        <v>46151.37106481481</v>
       </c>
       <c r="E34">
         <v>52227</v>
@@ -42620,7 +42620,7 @@
         <v>46151.3713222338</v>
       </c>
       <c r="D35" s="1">
-        <v>46151.621296296296</v>
+        <v>46151.371296296296</v>
       </c>
       <c r="E35">
         <v>51681</v>
@@ -42763,7 +42763,7 @@
         <v>46151.37147071759</v>
       </c>
       <c r="D36" s="1">
-        <v>46151.621412037035</v>
+        <v>46151.371412037035</v>
       </c>
       <c r="E36">
         <v>51338</v>
@@ -42906,7 +42906,7 @@
         <v>46151.3716993287</v>
       </c>
       <c r="D37" s="1">
-        <v>46151.62164351852</v>
+        <v>46151.37164351852</v>
       </c>
       <c r="E37">
         <v>50794</v>
@@ -43049,7 +43049,7 @@
         <v>46151.37181008102</v>
       </c>
       <c r="D38" s="1">
-        <v>46151.62175925926</v>
+        <v>46151.37175925926</v>
       </c>
       <c r="E38">
         <v>50458</v>
@@ -43192,7 +43192,7 @@
         <v>46151.372019201386</v>
       </c>
       <c r="D39" s="1">
-        <v>46151.62199074074</v>
+        <v>46151.37199074074</v>
       </c>
       <c r="E39">
         <v>49928</v>
@@ -43335,7 +43335,7 @@
         <v>46151.372164375</v>
       </c>
       <c r="D40" s="1">
-        <v>46151.62210648148</v>
+        <v>46151.37210648148</v>
       </c>
       <c r="E40">
         <v>49599</v>
@@ -43478,7 +43478,7 @@
         <v>46151.3723934375</v>
       </c>
       <c r="D41" s="1">
-        <v>46151.62233796297</v>
+        <v>46151.37233796297</v>
       </c>
       <c r="E41">
         <v>49097</v>
@@ -43621,7 +43621,7 @@
         <v>46151.372482060186</v>
       </c>
       <c r="D42" s="1">
-        <v>46151.622453703705</v>
+        <v>46151.372453703705</v>
       </c>
       <c r="E42">
         <v>48774</v>
@@ -43764,7 +43764,7 @@
         <v>46151.37271236111</v>
       </c>
       <c r="D43" s="1">
-        <v>46151.62268518518</v>
+        <v>46151.37268518518</v>
       </c>
       <c r="E43">
         <v>48261</v>
@@ -43907,7 +43907,7 @@
         <v>46151.37285802083</v>
       </c>
       <c r="D44" s="1">
-        <v>46151.62280092593</v>
+        <v>46151.37280092593</v>
       </c>
       <c r="E44">
         <v>47941</v>
@@ -44050,7 +44050,7 @@
         <v>46151.373087685184</v>
       </c>
       <c r="D45" s="1">
-        <v>46151.623032407406</v>
+        <v>46151.373032407406</v>
       </c>
       <c r="E45">
         <v>47463</v>
@@ -44193,7 +44193,7 @@
         <v>46151.373176030094</v>
       </c>
       <c r="D46" s="1">
-        <v>46151.623148148145</v>
+        <v>46151.373148148145</v>
       </c>
       <c r="E46">
         <v>47159</v>
@@ -44336,7 +44336,7 @@
         <v>46151.37340822916</v>
       </c>
       <c r="D47" s="1">
-        <v>46151.62337962963</v>
+        <v>46151.37337962963</v>
       </c>
       <c r="E47">
         <v>46687</v>
@@ -44479,7 +44479,7 @@
         <v>46151.373556412036</v>
       </c>
       <c r="D48" s="1">
-        <v>46151.62349537037</v>
+        <v>46151.37349537037</v>
       </c>
       <c r="E48">
         <v>46375</v>
@@ -44622,7 +44622,7 @@
         <v>46151.373783125</v>
       </c>
       <c r="D49" s="1">
-        <v>46151.62372685185</v>
+        <v>46151.37372685185</v>
       </c>
       <c r="E49">
         <v>45900</v>
@@ -44765,7 +44765,7 @@
         <v>46151.37387119213</v>
       </c>
       <c r="D50" s="1">
-        <v>46151.62384259259</v>
+        <v>46151.37384259259</v>
       </c>
       <c r="E50">
         <v>45587</v>
@@ -44908,7 +44908,7 @@
         <v>46151.37410142361</v>
       </c>
       <c r="D51" s="1">
-        <v>46151.624074074076</v>
+        <v>46151.374074074076</v>
       </c>
       <c r="E51">
         <v>45108</v>
@@ -45051,7 +45051,7 @@
         <v>46151.37424694445</v>
       </c>
       <c r="D52" s="1">
-        <v>46151.624189814815</v>
+        <v>46151.374189814815</v>
       </c>
       <c r="E52">
         <v>44798</v>
@@ -45194,7 +45194,7 @@
         <v>46151.37447869213</v>
       </c>
       <c r="D53" s="1">
-        <v>46151.6244212963</v>
+        <v>46151.3744212963</v>
       </c>
       <c r="E53">
         <v>44340</v>
@@ -45337,7 +45337,7 @@
         <v>46151.37456532408</v>
       </c>
       <c r="D54" s="1">
-        <v>46151.62453703704</v>
+        <v>46151.37453703704</v>
       </c>
       <c r="E54">
         <v>44025</v>
@@ -45480,7 +45480,7 @@
         <v>46151.37479625</v>
       </c>
       <c r="D55" s="1">
-        <v>46151.624768518515</v>
+        <v>46151.374768518515</v>
       </c>
       <c r="E55">
         <v>43574</v>
@@ -45623,7 +45623,7 @@
         <v>46151.374943310184</v>
       </c>
       <c r="D56" s="1">
-        <v>46151.62488425926</v>
+        <v>46151.37488425926</v>
       </c>
       <c r="E56">
         <v>43272</v>
@@ -45766,7 +45766,7 @@
         <v>46151.37517506944</v>
       </c>
       <c r="D57" s="1">
-        <v>46151.62511574074</v>
+        <v>46151.37511574074</v>
       </c>
       <c r="E57">
         <v>42838</v>
@@ -45909,7 +45909,7 @@
         <v>46151.375259768516</v>
       </c>
       <c r="D58" s="1">
-        <v>46151.625231481485</v>
+        <v>46151.375231481485</v>
       </c>
       <c r="E58">
         <v>42540</v>
@@ -46052,7 +46052,7 @@
         <v>46151.37549310185</v>
       </c>
       <c r="D59" s="1">
-        <v>46151.62546296296</v>
+        <v>46151.37546296296</v>
       </c>
       <c r="E59">
         <v>42106</v>
@@ -46195,7 +46195,7 @@
         <v>46151.3756371412</v>
       </c>
       <c r="D60" s="1">
-        <v>46151.6255787037</v>
+        <v>46151.3755787037</v>
       </c>
       <c r="E60">
         <v>41811</v>
@@ -46338,7 +46338,7 @@
         <v>46151.37586707176</v>
       </c>
       <c r="D61" s="1">
-        <v>46151.625810185185</v>
+        <v>46151.375810185185</v>
       </c>
       <c r="E61">
         <v>41380</v>
@@ -46481,7 +46481,7 @@
         <v>46151.3759543287</v>
       </c>
       <c r="D62" s="1">
-        <v>46151.625925925924</v>
+        <v>46151.375925925924</v>
       </c>
       <c r="E62">
         <v>41095</v>
@@ -46624,7 +46624,7 @@
         <v>46151.37618792824</v>
       </c>
       <c r="D63" s="1">
-        <v>46151.62615740741</v>
+        <v>46151.37615740741</v>
       </c>
       <c r="E63">
         <v>40689</v>
@@ -46767,7 +46767,7 @@
         <v>46151.37633047454</v>
       </c>
       <c r="D64" s="1">
-        <v>46151.62627314815</v>
+        <v>46151.37627314815</v>
       </c>
       <c r="E64">
         <v>40415</v>
@@ -46910,7 +46910,7 @@
         <v>46151.37656064815</v>
       </c>
       <c r="D65" s="1">
-        <v>46151.62650462963</v>
+        <v>46151.37650462963</v>
       </c>
       <c r="E65">
         <v>40025</v>
@@ -47053,7 +47053,7 @@
         <v>46151.376650266204</v>
       </c>
       <c r="D66" s="1">
-        <v>46151.62662037037</v>
+        <v>46151.37662037037</v>
       </c>
       <c r="E66">
         <v>39768</v>
@@ -47196,7 +47196,7 @@
         <v>46151.37687918982</v>
       </c>
       <c r="D67" s="1">
-        <v>46151.626851851855</v>
+        <v>46151.376851851855</v>
       </c>
       <c r="E67">
         <v>39409</v>
@@ -47339,7 +47339,7 @@
         <v>46151.377025381946</v>
       </c>
       <c r="D68" s="1">
-        <v>46151.626967592594</v>
+        <v>46151.376967592594</v>
       </c>
       <c r="E68">
         <v>39157</v>
@@ -47482,7 +47482,7 @@
         <v>46151.377256203705</v>
       </c>
       <c r="D69" s="1">
-        <v>46151.62719907407</v>
+        <v>46151.37719907407</v>
       </c>
       <c r="E69">
         <v>38814</v>
@@ -47625,7 +47625,7 @@
         <v>46151.37734407408</v>
       </c>
       <c r="D70" s="1">
-        <v>46151.62731481482</v>
+        <v>46151.37731481482</v>
       </c>
       <c r="E70">
         <v>38564</v>
@@ -47768,7 +47768,7 @@
         <v>46151.377574212966</v>
       </c>
       <c r="D71" s="1">
-        <v>46151.627546296295</v>
+        <v>46151.377546296295</v>
       </c>
       <c r="E71">
         <v>38218</v>
@@ -47911,7 +47911,7 @@
         <v>46151.37771826389</v>
       </c>
       <c r="D72" s="1">
-        <v>46151.62766203703</v>
+        <v>46151.37766203703</v>
       </c>
       <c r="E72">
         <v>37961</v>
@@ -48054,7 +48054,7 @@
         <v>46151.37795112268</v>
       </c>
       <c r="D73" s="1">
-        <v>46151.62789351852</v>
+        <v>46151.37789351852</v>
       </c>
       <c r="E73">
         <v>37611</v>
@@ -48197,7 +48197,7 @@
         <v>46151.37803966435</v>
       </c>
       <c r="D74" s="1">
-        <v>46151.62800925926</v>
+        <v>46151.37800925926</v>
       </c>
       <c r="E74">
         <v>37359</v>
@@ -48340,7 +48340,7 @@
         <v>46151.37827043982</v>
       </c>
       <c r="D75" s="1">
-        <v>46151.62824074074</v>
+        <v>46151.37824074074</v>
       </c>
       <c r="E75">
         <v>37008</v>
@@ -48483,7 +48483,7 @@
         <v>46151.378413391205</v>
       </c>
       <c r="D76" s="1">
-        <v>46151.62835648148</v>
+        <v>46151.37835648148</v>
       </c>
       <c r="E76">
         <v>36753</v>
@@ -48626,7 +48626,7 @@
         <v>46151.37864724537</v>
       </c>
       <c r="D77" s="1">
-        <v>46151.628587962965</v>
+        <v>46151.378587962965</v>
       </c>
       <c r="E77">
         <v>36401</v>
@@ -48769,7 +48769,7 @@
         <v>46151.37873193287</v>
       </c>
       <c r="D78" s="1">
-        <v>46151.628703703704</v>
+        <v>46151.378703703704</v>
       </c>
       <c r="E78">
         <v>36145</v>
@@ -48912,7 +48912,7 @@
         <v>46151.378965219905</v>
       </c>
       <c r="D79" s="1">
-        <v>46151.62893518519</v>
+        <v>46151.37893518519</v>
       </c>
       <c r="E79">
         <v>35807</v>
@@ -49055,7 +49055,7 @@
         <v>46151.37910798611</v>
       </c>
       <c r="D80" s="1">
-        <v>46151.62905092593</v>
+        <v>46151.37905092593</v>
       </c>
       <c r="E80">
         <v>35566</v>
@@ -49198,7 +49198,7 @@
         <v>46151.37933956018</v>
       </c>
       <c r="D81" s="1">
-        <v>46151.629282407404</v>
+        <v>46151.379282407404</v>
       </c>
       <c r="E81">
         <v>35242</v>
@@ -49341,7 +49341,7 @@
         <v>46151.37942719908</v>
       </c>
       <c r="D82" s="1">
-        <v>46151.62939814815</v>
+        <v>46151.37939814815</v>
       </c>
       <c r="E82">
         <v>35012</v>
@@ -49484,7 +49484,7 @@
         <v>46151.37965768518</v>
       </c>
       <c r="D83" s="1">
-        <v>46151.62962962963</v>
+        <v>46151.37962962963</v>
       </c>
       <c r="E83">
         <v>34700</v>
@@ -49627,7 +49627,7 @@
         <v>46151.379805219905</v>
       </c>
       <c r="D84" s="1">
-        <v>46151.629745370374</v>
+        <v>46151.379745370374</v>
       </c>
       <c r="E84">
         <v>34444</v>
@@ -49770,7 +49770,7 @@
         <v>46151.380034560185</v>
       </c>
       <c r="D85" s="1">
-        <v>46151.62997685185</v>
+        <v>46151.37997685185</v>
       </c>
       <c r="E85">
         <v>34053</v>
@@ -49913,7 +49913,7 @@
         <v>46151.38012135417</v>
       </c>
       <c r="D86" s="1">
-        <v>46151.63009259259</v>
+        <v>46151.38009259259</v>
       </c>
       <c r="E86">
         <v>33785</v>
@@ -50056,7 +50056,7 @@
         <v>46151.38035240741</v>
       </c>
       <c r="D87" s="1">
-        <v>46151.630324074074</v>
+        <v>46151.380324074074</v>
       </c>
       <c r="E87">
         <v>33405</v>
@@ -50199,7 +50199,7 @@
         <v>46151.380500405096</v>
       </c>
       <c r="D88" s="1">
-        <v>46151.63043981481</v>
+        <v>46151.38043981481</v>
       </c>
       <c r="E88">
         <v>33162</v>
@@ -50342,7 +50342,7 @@
         <v>46151.380729606484</v>
       </c>
       <c r="D89" s="1">
-        <v>46151.6306712963</v>
+        <v>46151.3806712963</v>
       </c>
       <c r="E89">
         <v>32791</v>
@@ -50485,7 +50485,7 @@
         <v>46151.38081548611</v>
       </c>
       <c r="D90" s="1">
-        <v>46151.63078703704</v>
+        <v>46151.38078703704</v>
       </c>
       <c r="E90">
         <v>32574</v>
@@ -50628,7 +50628,7 @@
         <v>46151.38104910879</v>
       </c>
       <c r="D91" s="1">
-        <v>46151.63101851852</v>
+        <v>46151.38101851852</v>
       </c>
       <c r="E91">
         <v>32292</v>
@@ -50771,7 +50771,7 @@
         <v>46151.38119128472</v>
       </c>
       <c r="D92" s="1">
-        <v>46151.63113425926</v>
+        <v>46151.38113425926</v>
       </c>
       <c r="E92">
         <v>32085</v>
@@ -50914,7 +50914,7 @@
         <v>46151.38151011574</v>
       </c>
       <c r="D93" s="1">
-        <v>46151.63148148148</v>
+        <v>46151.38148148148</v>
       </c>
       <c r="E93">
         <v>31606</v>
@@ -51057,7 +51057,7 @@
         <v>46151.38174025463</v>
       </c>
       <c r="D94" s="1">
-        <v>46151.63171296296</v>
+        <v>46151.38171296296</v>
       </c>
       <c r="E94">
         <v>31327</v>
@@ -51200,7 +51200,7 @@
         <v>46151.38188641204</v>
       </c>
       <c r="D95" s="1">
-        <v>46151.63182870371</v>
+        <v>46151.38182870371</v>
       </c>
       <c r="E95">
         <v>31109</v>
@@ -51343,7 +51343,7 @@
         <v>46151.38212123843</v>
       </c>
       <c r="D96" s="1">
-        <v>46151.632060185184</v>
+        <v>46151.382060185184</v>
       </c>
       <c r="E96">
         <v>30782</v>
@@ -51486,7 +51486,7 @@
         <v>46151.38220516204</v>
       </c>
       <c r="D97" s="1">
-        <v>46151.63217592592</v>
+        <v>46151.38217592592</v>
       </c>
       <c r="E97">
         <v>30571</v>
@@ -51629,7 +51629,7 @@
         <v>46151.38243525463</v>
       </c>
       <c r="D98" s="1">
-        <v>46151.63240740741</v>
+        <v>46151.38240740741</v>
       </c>
       <c r="E98">
         <v>30233</v>
@@ -51772,7 +51772,7 @@
         <v>46151.38258096065</v>
       </c>
       <c r="D99" s="1">
-        <v>46151.632523148146</v>
+        <v>46151.382523148146</v>
       </c>
       <c r="E99">
         <v>29967</v>
@@ -51915,7 +51915,7 @@
         <v>46151.382811400465</v>
       </c>
       <c r="D100" s="1">
-        <v>46151.63275462963</v>
+        <v>46151.38275462963</v>
       </c>
       <c r="E100">
         <v>29666</v>
@@ -52058,7 +52058,7 @@
         <v>46151.382898888885</v>
       </c>
       <c r="D101" s="1">
-        <v>46151.63287037037</v>
+        <v>46151.38287037037</v>
       </c>
       <c r="E101">
         <v>29432</v>
@@ -52201,7 +52201,7 @@
         <v>46151.38313048611</v>
       </c>
       <c r="D102" s="1">
-        <v>46151.633101851854</v>
+        <v>46151.383101851854</v>
       </c>
       <c r="E102">
         <v>29112</v>
@@ -52344,7 +52344,7 @@
         <v>46151.383275416665</v>
       </c>
       <c r="D103" s="1">
-        <v>46151.63321759259</v>
+        <v>46151.38321759259</v>
       </c>
       <c r="E103">
         <v>28885</v>
@@ -52487,7 +52487,7 @@
         <v>46151.38350782407</v>
       </c>
       <c r="D104" s="1">
-        <v>46151.63344907408</v>
+        <v>46151.38344907408</v>
       </c>
       <c r="E104">
         <v>28592</v>
@@ -52630,7 +52630,7 @@
         <v>46151.38359453704</v>
       </c>
       <c r="D105" s="1">
-        <v>46151.633564814816</v>
+        <v>46151.383564814816</v>
       </c>
       <c r="E105">
         <v>28376</v>
@@ -52773,7 +52773,7 @@
         <v>46151.38382377315</v>
       </c>
       <c r="D106" s="1">
-        <v>46151.63379629629</v>
+        <v>46151.38379629629</v>
       </c>
       <c r="E106">
         <v>28081</v>
@@ -52916,7 +52916,7 @@
         <v>46151.38397230324</v>
       </c>
       <c r="D107" s="1">
-        <v>46151.63391203704</v>
+        <v>46151.38391203704</v>
       </c>
       <c r="E107">
         <v>27853</v>
@@ -53059,7 +53059,7 @@
         <v>46151.38420046296</v>
       </c>
       <c r="D108" s="1">
-        <v>46151.63414351852</v>
+        <v>46151.38414351852</v>
       </c>
       <c r="E108">
         <v>27563</v>
@@ -53202,7 +53202,7 @@
         <v>46151.384288298614</v>
       </c>
       <c r="D109" s="1">
-        <v>46151.63425925926</v>
+        <v>46151.38425925926</v>
       </c>
       <c r="E109">
         <v>27343</v>
@@ -53345,7 +53345,7 @@
         <v>46151.38451960648</v>
       </c>
       <c r="D110" s="1">
-        <v>46151.63449074074</v>
+        <v>46151.38449074074</v>
       </c>
       <c r="E110">
         <v>27059</v>
@@ -53488,7 +53488,7 @@
         <v>46151.384664756944</v>
       </c>
       <c r="D111" s="1">
-        <v>46151.63460648148</v>
+        <v>46151.38460648148</v>
       </c>
       <c r="E111">
         <v>26833</v>
@@ -53631,7 +53631,7 @@
         <v>46151.384895138886</v>
       </c>
       <c r="D112" s="1">
-        <v>46151.63483796296</v>
+        <v>46151.38483796296</v>
       </c>
       <c r="E112">
         <v>26525</v>
@@ -53774,7 +53774,7 @@
         <v>46151.384982372685</v>
       </c>
       <c r="D113" s="1">
-        <v>46151.6349537037</v>
+        <v>46151.3849537037</v>
       </c>
       <c r="E113">
         <v>26293</v>
@@ -53917,7 +53917,7 @@
         <v>46151.38521412037</v>
       </c>
       <c r="D114" s="1">
-        <v>46151.63518518519</v>
+        <v>46151.38518518519</v>
       </c>
       <c r="E114">
         <v>25976</v>
@@ -54060,7 +54060,7 @@
         <v>46151.385360532404</v>
       </c>
       <c r="D115" s="1">
-        <v>46151.635300925926</v>
+        <v>46151.385300925926</v>
       </c>
       <c r="E115">
         <v>25735</v>
@@ -54203,7 +54203,7 @@
         <v>46151.385591122686</v>
       </c>
       <c r="D116" s="1">
-        <v>46151.63553240741</v>
+        <v>46151.38553240741</v>
       </c>
       <c r="E116">
         <v>25409</v>
@@ -54346,7 +54346,7 @@
         <v>46151.38567679398</v>
       </c>
       <c r="D117" s="1">
-        <v>46151.63564814815</v>
+        <v>46151.38564814815</v>
       </c>
       <c r="E117">
         <v>25175</v>
@@ -54489,7 +54489,7 @@
         <v>46151.38590797454</v>
       </c>
       <c r="D118" s="1">
-        <v>46151.635879629626</v>
+        <v>46151.385879629626</v>
       </c>
       <c r="E118">
         <v>24858</v>
@@ -54632,7 +54632,7 @@
         <v>46151.38605569444</v>
       </c>
       <c r="D119" s="1">
-        <v>46151.63599537037</v>
+        <v>46151.38599537037</v>
       </c>
       <c r="E119">
         <v>24629</v>
@@ -54775,7 +54775,7 @@
         <v>46151.38628791667</v>
       </c>
       <c r="D120" s="1">
-        <v>46151.63622685185</v>
+        <v>46151.38622685185</v>
       </c>
       <c r="E120">
         <v>24344</v>
@@ -54918,7 +54918,7 @@
         <v>46151.386371458335</v>
       </c>
       <c r="D121" s="1">
-        <v>46151.636342592596</v>
+        <v>46151.386342592596</v>
       </c>
       <c r="E121">
         <v>24115</v>
@@ -55061,7 +55061,7 @@
         <v>46151.386603287036</v>
       </c>
       <c r="D122" s="1">
-        <v>46151.63657407407</v>
+        <v>46151.38657407407</v>
       </c>
       <c r="E122">
         <v>23816</v>
@@ -55204,7 +55204,7 @@
         <v>46151.38675087963</v>
       </c>
       <c r="D123" s="1">
-        <v>46151.63668981481</v>
+        <v>46151.38668981481</v>
       </c>
       <c r="E123">
         <v>23599</v>
@@ -55347,7 +55347,7 @@
         <v>46151.386980243056</v>
       </c>
       <c r="D124" s="1">
-        <v>46151.636921296296</v>
+        <v>46151.386921296296</v>
       </c>
       <c r="E124">
         <v>23309</v>
@@ -55490,7 +55490,7 @@
         <v>46151.38706799768</v>
       </c>
       <c r="D125" s="1">
-        <v>46151.637037037035</v>
+        <v>46151.387037037035</v>
       </c>
       <c r="E125">
         <v>23093</v>
@@ -55633,7 +55633,7 @@
         <v>46151.38729949074</v>
       </c>
       <c r="D126" s="1">
-        <v>46151.63726851852</v>
+        <v>46151.38726851852</v>
       </c>
       <c r="E126">
         <v>22815</v>
@@ -55776,7 +55776,7 @@
         <v>46151.38744532407</v>
       </c>
       <c r="D127" s="1">
-        <v>46151.63738425926</v>
+        <v>46151.38738425926</v>
       </c>
       <c r="E127">
         <v>22599</v>
@@ -55919,7 +55919,7 @@
         <v>46151.38767321759</v>
       </c>
       <c r="D128" s="1">
-        <v>46151.63761574074</v>
+        <v>46151.38761574074</v>
       </c>
       <c r="E128">
         <v>22322</v>
@@ -56062,7 +56062,7 @@
         <v>46151.38799190972</v>
       </c>
       <c r="D129" s="1">
-        <v>46151.63796296297</v>
+        <v>46151.38796296297</v>
       </c>
       <c r="E129">
         <v>21826</v>
@@ -56205,7 +56205,7 @@
         <v>46151.38813681713</v>
       </c>
       <c r="D130" s="1">
-        <v>46151.638078703705</v>
+        <v>46151.388078703705</v>
       </c>
       <c r="E130">
         <v>21613</v>
@@ -56348,7 +56348,7 @@
         <v>46151.38836872685</v>
       </c>
       <c r="D131" s="1">
-        <v>46151.63831018518</v>
+        <v>46151.38831018518</v>
       </c>
       <c r="E131">
         <v>21333</v>
@@ -56491,7 +56491,7 @@
         <v>46151.3884569213</v>
       </c>
       <c r="D132" s="1">
-        <v>46151.63842592593</v>
+        <v>46151.38842592593</v>
       </c>
       <c r="E132">
         <v>21116</v>
@@ -56634,7 +56634,7 @@
         <v>46151.388686736114</v>
       </c>
       <c r="D133" s="1">
-        <v>46151.638657407406</v>
+        <v>46151.388657407406</v>
       </c>
       <c r="E133">
         <v>20842</v>
@@ -56777,7 +56777,7 @@
         <v>46151.38883111111</v>
       </c>
       <c r="D134" s="1">
-        <v>46151.638773148145</v>
+        <v>46151.388773148145</v>
       </c>
       <c r="E134">
         <v>20630</v>
@@ -56920,7 +56920,7 @@
         <v>46151.38906603009</v>
       </c>
       <c r="D135" s="1">
-        <v>46151.63900462963</v>
+        <v>46151.38900462963</v>
       </c>
       <c r="E135">
         <v>20369</v>
@@ -57063,7 +57063,7 @@
         <v>46151.38914893519</v>
       </c>
       <c r="D136" s="1">
-        <v>46151.63912037037</v>
+        <v>46151.38912037037</v>
       </c>
       <c r="E136">
         <v>20165</v>
@@ -57206,7 +57206,7 @@
         <v>46151.38938108796</v>
       </c>
       <c r="D137" s="1">
-        <v>46151.63935185185</v>
+        <v>46151.38935185185</v>
       </c>
       <c r="E137">
         <v>19917</v>
@@ -57349,7 +57349,7 @@
         <v>46151.389525439816</v>
       </c>
       <c r="D138" s="1">
-        <v>46151.63946759259</v>
+        <v>46151.38946759259</v>
       </c>
       <c r="E138">
         <v>19722</v>
@@ -57492,7 +57492,7 @@
         <v>46151.389845868056</v>
       </c>
       <c r="D139" s="1">
-        <v>46151.639814814815</v>
+        <v>46151.389814814815</v>
       </c>
       <c r="E139">
         <v>19295</v>
@@ -57635,7 +57635,7 @@
         <v>46151.39007819445</v>
       </c>
       <c r="D140" s="1">
-        <v>46151.6400462963</v>
+        <v>46151.3900462963</v>
       </c>
       <c r="E140">
         <v>19069</v>
@@ -57778,7 +57778,7 @@
         <v>46151.39022167824</v>
       </c>
       <c r="D141" s="1">
-        <v>46151.64016203704</v>
+        <v>46151.39016203704</v>
       </c>
       <c r="E141">
         <v>18880</v>
@@ -57921,7 +57921,7 @@
         <v>46151.39045153935</v>
       </c>
       <c r="D142" s="1">
-        <v>46151.640393518515</v>
+        <v>46151.390393518515</v>
       </c>
       <c r="E142">
         <v>18660</v>
@@ -58064,7 +58064,7 @@
         <v>46151.39053790509</v>
       </c>
       <c r="D143" s="1">
-        <v>46151.64050925926</v>
+        <v>46151.39050925926</v>
       </c>
       <c r="E143">
         <v>18471</v>
@@ -58207,7 +58207,7 @@
         <v>46151.3907740625</v>
       </c>
       <c r="D144" s="1">
-        <v>46151.64074074074</v>
+        <v>46151.39074074074</v>
       </c>
       <c r="E144">
         <v>18257</v>
@@ -58350,7 +58350,7 @@
         <v>46151.390914780095</v>
       </c>
       <c r="D145" s="1">
-        <v>46151.640856481485</v>
+        <v>46151.390856481485</v>
       </c>
       <c r="E145">
         <v>18074</v>
@@ -58493,7 +58493,7 @@
         <v>46151.39114673611</v>
       </c>
       <c r="D146" s="1">
-        <v>46151.64108796296</v>
+        <v>46151.39108796296</v>
       </c>
       <c r="E146">
         <v>17866</v>
@@ -58636,7 +58636,7 @@
         <v>46151.39123313657</v>
       </c>
       <c r="D147" s="1">
-        <v>46151.6412037037</v>
+        <v>46151.3912037037</v>
       </c>
       <c r="E147">
         <v>17690</v>
@@ -58779,7 +58779,7 @@
         <v>46151.39146528935</v>
       </c>
       <c r="D148" s="1">
-        <v>46151.641435185185</v>
+        <v>46151.391435185185</v>
       </c>
       <c r="E148">
         <v>17482</v>
@@ -58922,7 +58922,7 @@
         <v>46151.39160857639</v>
       </c>
       <c r="D149" s="1">
-        <v>46151.641550925924</v>
+        <v>46151.391550925924</v>
       </c>
       <c r="E149">
         <v>17310</v>
@@ -59065,7 +59065,7 @@
         <v>46151.391840613425</v>
       </c>
       <c r="D150" s="1">
-        <v>46151.64178240741</v>
+        <v>46151.39178240741</v>
       </c>
       <c r="E150">
         <v>17117</v>
@@ -59208,7 +59208,7 @@
         <v>46151.39192763889</v>
       </c>
       <c r="D151" s="1">
-        <v>46151.64189814815</v>
+        <v>46151.39189814815</v>
       </c>
       <c r="E151">
         <v>16942</v>
@@ -59351,7 +59351,7 @@
         <v>46151.39215925926</v>
       </c>
       <c r="D152" s="1">
-        <v>46151.64212962963</v>
+        <v>46151.39212962963</v>
       </c>
       <c r="E152">
         <v>16729</v>
@@ -59494,7 +59494,7 @@
         <v>46151.39230315972</v>
       </c>
       <c r="D153" s="1">
-        <v>46151.64224537037</v>
+        <v>46151.39224537037</v>
       </c>
       <c r="E153">
         <v>16548</v>
@@ -59637,7 +59637,7 @@
         <v>46151.392535439816</v>
       </c>
       <c r="D154" s="1">
-        <v>46151.642476851855</v>
+        <v>46151.392476851855</v>
       </c>
       <c r="E154">
         <v>16320</v>
@@ -59780,7 +59780,7 @@
         <v>46151.39262252315</v>
       </c>
       <c r="D155" s="1">
-        <v>46151.642592592594</v>
+        <v>46151.392592592594</v>
       </c>
       <c r="E155">
         <v>16131</v>
@@ -59923,7 +59923,7 @@
         <v>46151.39285366898</v>
       </c>
       <c r="D156" s="1">
-        <v>46151.64282407407</v>
+        <v>46151.39282407407</v>
       </c>
       <c r="E156">
         <v>15900</v>
@@ -60066,7 +60066,7 @@
         <v>46151.39299847222</v>
       </c>
       <c r="D157" s="1">
-        <v>46151.64293981482</v>
+        <v>46151.39293981482</v>
       </c>
       <c r="E157">
         <v>15708</v>
@@ -60209,7 +60209,7 @@
         <v>46151.39323050926</v>
       </c>
       <c r="D158" s="1">
-        <v>46151.643171296295</v>
+        <v>46151.393171296295</v>
       </c>
       <c r="E158">
         <v>15450</v>
@@ -60352,7 +60352,7 @@
         <v>46151.39331652778</v>
       </c>
       <c r="D159" s="1">
-        <v>46151.64328703703</v>
+        <v>46151.39328703703</v>
       </c>
       <c r="E159">
         <v>15250</v>
@@ -60495,7 +60495,7 @@
         <v>46151.393548935186</v>
       </c>
       <c r="D160" s="1">
-        <v>46151.64351851852</v>
+        <v>46151.39351851852</v>
       </c>
       <c r="E160">
         <v>14993</v>
@@ -60638,7 +60638,7 @@
         <v>46151.3936934375</v>
       </c>
       <c r="D161" s="1">
-        <v>46151.64363425926</v>
+        <v>46151.39363425926</v>
       </c>
       <c r="E161">
         <v>14788</v>
@@ -60781,7 +60781,7 @@
         <v>46151.393924606484</v>
       </c>
       <c r="D162" s="1">
-        <v>46151.64386574074</v>
+        <v>46151.39386574074</v>
       </c>
       <c r="E162">
         <v>14553</v>
@@ -60924,7 +60924,7 @@
         <v>46151.39424314815</v>
       </c>
       <c r="D163" s="1">
-        <v>46151.644212962965</v>
+        <v>46151.394212962965</v>
       </c>
       <c r="E163">
         <v>14082</v>
@@ -61067,7 +61067,7 @@
         <v>46151.394386712964</v>
       </c>
       <c r="D164" s="1">
-        <v>46151.644328703704</v>
+        <v>46151.394328703704</v>
       </c>
       <c r="E164">
         <v>13899</v>
@@ -61210,7 +61210,7 @@
         <v>46151.394619224535</v>
       </c>
       <c r="D165" s="1">
-        <v>46151.64456018519</v>
+        <v>46151.39456018519</v>
       </c>
       <c r="E165">
         <v>13680</v>
@@ -61353,7 +61353,7 @@
         <v>46151.39470539352</v>
       </c>
       <c r="D166" s="1">
-        <v>46151.64467592593</v>
+        <v>46151.39467592593</v>
       </c>
       <c r="E166">
         <v>13495</v>
@@ -61496,7 +61496,7 @@
         <v>46151.394937164354</v>
       </c>
       <c r="D167" s="1">
-        <v>46151.644907407404</v>
+        <v>46151.394907407404</v>
       </c>
       <c r="E167">
         <v>13278</v>
@@ -61639,7 +61639,7 @@
         <v>46151.39508425926</v>
       </c>
       <c r="D168" s="1">
-        <v>46151.64502314815</v>
+        <v>46151.39502314815</v>
       </c>
       <c r="E168">
         <v>13105</v>
@@ -61782,7 +61782,7 @@
         <v>46151.39531435185</v>
       </c>
       <c r="D169" s="1">
-        <v>46151.64525462963</v>
+        <v>46151.39525462963</v>
       </c>
       <c r="E169">
         <v>12890</v>
@@ -61925,7 +61925,7 @@
         <v>46151.395400497684</v>
       </c>
       <c r="D170" s="1">
-        <v>46151.645370370374</v>
+        <v>46151.395370370374</v>
       </c>
       <c r="E170">
         <v>12706</v>
@@ -62068,7 +62068,7 @@
         <v>46151.39563255787</v>
       </c>
       <c r="D171" s="1">
-        <v>46151.64560185185</v>
+        <v>46151.39560185185</v>
       </c>
       <c r="E171">
         <v>12465</v>
@@ -62211,7 +62211,7 @@
         <v>46151.39577701389</v>
       </c>
       <c r="D172" s="1">
-        <v>46151.64571759259</v>
+        <v>46151.39571759259</v>
       </c>
       <c r="E172">
         <v>12257</v>
@@ -62354,7 +62354,7 @@
         <v>46151.396008171294</v>
       </c>
       <c r="D173" s="1">
-        <v>46151.645949074074</v>
+        <v>46151.395949074074</v>
       </c>
       <c r="E173">
         <v>12001</v>
@@ -62497,7 +62497,7 @@
         <v>46151.39609361111</v>
       </c>
       <c r="D174" s="1">
-        <v>46151.64606481481</v>
+        <v>46151.39606481481</v>
       </c>
       <c r="E174">
         <v>11799</v>
@@ -62640,7 +62640,7 @@
         <v>46151.396331805554</v>
       </c>
       <c r="D175" s="1">
-        <v>46151.6462962963</v>
+        <v>46151.3962962963</v>
       </c>
       <c r="E175">
         <v>11553</v>
@@ -62783,7 +62783,7 @@
         <v>46151.39647280092</v>
       </c>
       <c r="D176" s="1">
-        <v>46151.64641203704</v>
+        <v>46151.39641203704</v>
       </c>
       <c r="E176">
         <v>11364</v>
@@ -62926,7 +62926,7 @@
         <v>46151.39670331019</v>
       </c>
       <c r="D177" s="1">
-        <v>46151.64664351852</v>
+        <v>46151.39664351852</v>
       </c>
       <c r="E177">
         <v>11127</v>
@@ -63069,7 +63069,7 @@
         <v>46151.39679532407</v>
       </c>
       <c r="D178" s="1">
-        <v>46151.64675925926</v>
+        <v>46151.39675925926</v>
       </c>
       <c r="E178">
         <v>10943</v>
@@ -63212,7 +63212,7 @@
         <v>46151.397022083336</v>
       </c>
       <c r="D179" s="1">
-        <v>46151.64699074074</v>
+        <v>46151.39699074074</v>
       </c>
       <c r="E179">
         <v>10715</v>
@@ -63355,7 +63355,7 @@
         <v>46151.39716914352</v>
       </c>
       <c r="D180" s="1">
-        <v>46151.64710648148</v>
+        <v>46151.39710648148</v>
       </c>
       <c r="E180">
         <v>10529</v>
@@ -63498,7 +63498,7 @@
         <v>46151.39740458333</v>
       </c>
       <c r="D181" s="1">
-        <v>46151.64733796296</v>
+        <v>46151.39733796296</v>
       </c>
       <c r="E181">
         <v>10315</v>
@@ -63641,7 +63641,7 @@
         <v>46151.397490428244</v>
       </c>
       <c r="D182" s="1">
-        <v>46151.64745370371</v>
+        <v>46151.39745370371</v>
       </c>
       <c r="E182">
         <v>10135</v>
@@ -63784,7 +63784,7 @@
         <v>46151.39772152778</v>
       </c>
       <c r="D183" s="1">
-        <v>46151.647685185184</v>
+        <v>46151.397685185184</v>
       </c>
       <c r="E183">
         <v>9925</v>
@@ -63927,7 +63927,7 @@
         <v>46151.397864224535</v>
       </c>
       <c r="D184" s="1">
-        <v>46151.64780092592</v>
+        <v>46151.39780092592</v>
       </c>
       <c r="E184">
         <v>9743</v>
@@ -64070,7 +64070,7 @@
         <v>46151.39810280093</v>
       </c>
       <c r="D185" s="1">
-        <v>46151.64803240741</v>
+        <v>46151.39803240741</v>
       </c>
       <c r="E185">
         <v>9527</v>
@@ -64213,7 +64213,7 @@
         <v>46151.39818405093</v>
       </c>
       <c r="D186" s="1">
-        <v>46151.648148148146</v>
+        <v>46151.398148148146</v>
       </c>
       <c r="E186">
         <v>9349</v>
@@ -64356,7 +64356,7 @@
         <v>46151.39841559028</v>
       </c>
       <c r="D187" s="1">
-        <v>46151.64837962963</v>
+        <v>46151.39837962963</v>
       </c>
       <c r="E187">
         <v>9140</v>
@@ -64499,7 +64499,7 @@
         <v>46151.39879309028</v>
       </c>
       <c r="D188" s="1">
-        <v>46151.648726851854</v>
+        <v>46151.398726851854</v>
       </c>
       <c r="E188">
         <v>8747</v>
@@ -64642,7 +64642,7 @@
         <v>46151.39887917824</v>
       </c>
       <c r="D189" s="1">
-        <v>46151.64884259259</v>
+        <v>46151.39884259259</v>
       </c>
       <c r="E189">
         <v>8566</v>
@@ -64785,7 +64785,7 @@
         <v>46151.39911207176</v>
       </c>
       <c r="D190" s="1">
-        <v>46151.64907407408</v>
+        <v>46151.39907407408</v>
       </c>
       <c r="E190">
         <v>8361</v>
@@ -64928,7 +64928,7 @@
         <v>46151.39925440972</v>
       </c>
       <c r="D191" s="1">
-        <v>46151.649189814816</v>
+        <v>46151.399189814816</v>
       </c>
       <c r="E191">
         <v>8187</v>
@@ -65071,7 +65071,7 @@
         <v>46151.39948543981</v>
       </c>
       <c r="D192" s="1">
-        <v>46151.64942129629</v>
+        <v>46151.39942129629</v>
       </c>
       <c r="E192">
         <v>7983</v>
@@ -65214,7 +65214,7 @@
         <v>46151.399573414354</v>
       </c>
       <c r="D193" s="1">
-        <v>46151.64953703704</v>
+        <v>46151.39953703704</v>
       </c>
       <c r="E193">
         <v>7808</v>
@@ -65357,7 +65357,7 @@
         <v>46151.3998050463</v>
       </c>
       <c r="D194" s="1">
-        <v>46151.64976851852</v>
+        <v>46151.39976851852</v>
       </c>
       <c r="E194">
         <v>7605</v>
@@ -65500,7 +65500,7 @@
         <v>46151.39994849537</v>
       </c>
       <c r="D195" s="1">
-        <v>46151.64988425926</v>
+        <v>46151.39988425926</v>
       </c>
       <c r="E195">
         <v>7434</v>
@@ -65643,7 +65643,7 @@
         <v>46151.40018239583</v>
       </c>
       <c r="D196" s="1">
-        <v>46151.65011574074</v>
+        <v>46151.40011574074</v>
       </c>
       <c r="E196">
         <v>7230</v>
@@ -65786,7 +65786,7 @@
         <v>46151.40026785879</v>
       </c>
       <c r="D197" s="1">
-        <v>46151.65023148148</v>
+        <v>46151.40023148148</v>
       </c>
       <c r="E197">
         <v>7060</v>
@@ -65929,7 +65929,7 @@
         <v>46151.40049945602</v>
       </c>
       <c r="D198" s="1">
-        <v>46151.65046296296</v>
+        <v>46151.40046296296</v>
       </c>
       <c r="E198">
         <v>6861</v>
@@ -66072,7 +66072,7 @@
         <v>46151.40064368056</v>
       </c>
       <c r="D199" s="1">
-        <v>46151.6505787037</v>
+        <v>46151.4005787037</v>
       </c>
       <c r="E199">
         <v>6689</v>
@@ -66215,7 +66215,7 @@
         <v>46151.40087175926</v>
       </c>
       <c r="D200" s="1">
-        <v>46151.65081018519</v>
+        <v>46151.40081018519</v>
       </c>
       <c r="E200">
         <v>6503</v>
@@ -66358,7 +66358,7 @@
         <v>46151.400962210646</v>
       </c>
       <c r="D201" s="1">
-        <v>46151.650925925926</v>
+        <v>46151.400925925926</v>
       </c>
       <c r="E201">
         <v>6339</v>
@@ -66501,7 +66501,7 @@
         <v>46151.40119469907</v>
       </c>
       <c r="D202" s="1">
-        <v>46151.65115740741</v>
+        <v>46151.40115740741</v>
       </c>
       <c r="E202">
         <v>6131</v>
@@ -66644,7 +66644,7 @@
         <v>46151.40133850694</v>
       </c>
       <c r="D203" s="1">
-        <v>46151.65127314815</v>
+        <v>46151.40127314815</v>
       </c>
       <c r="E203">
         <v>5966</v>
@@ -66787,7 +66787,7 @@
         <v>46151.40157212963</v>
       </c>
       <c r="D204" s="1">
-        <v>46151.651504629626</v>
+        <v>46151.401504629626</v>
       </c>
       <c r="E204">
         <v>5763</v>
@@ -66930,7 +66930,7 @@
         <v>46151.40165837963</v>
       </c>
       <c r="D205" s="1">
-        <v>46151.65162037037</v>
+        <v>46151.40162037037</v>
       </c>
       <c r="E205">
         <v>5589</v>
@@ -67073,7 +67073,7 @@
         <v>46151.40188953704</v>
       </c>
       <c r="D206" s="1">
-        <v>46151.65185185185</v>
+        <v>46151.40185185185</v>
       </c>
       <c r="E206">
         <v>5375</v>
@@ -67216,7 +67216,7 @@
         <v>46151.40203293981</v>
       </c>
       <c r="D207" s="1">
-        <v>46151.651967592596</v>
+        <v>46151.401967592596</v>
       </c>
       <c r="E207">
         <v>5185</v>
@@ -67359,7 +67359,7 @@
         <v>46151.40620074074</v>
       </c>
       <c r="D208" s="1">
-        <v>46151.65613425926</v>
+        <v>46151.40613425926</v>
       </c>
       <c r="E208">
         <v>4824</v>
